--- a/Python/results/metrics_data.xlsx
+++ b/Python/results/metrics_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4921" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6127" uniqueCount="514">
   <si>
     <t>Pattern</t>
   </si>
@@ -1381,6 +1381,180 @@
   </si>
   <si>
     <t>20250707_121101</t>
+  </si>
+  <si>
+    <t>2025-07-14 17:09:56</t>
+  </si>
+  <si>
+    <t>569.2933333333333</t>
+  </si>
+  <si>
+    <t>1.8976444444444445</t>
+  </si>
+  <si>
+    <t>21773134.44074074</t>
+  </si>
+  <si>
+    <t>73977990.06296296</t>
+  </si>
+  <si>
+    <t>70616916.84074074</t>
+  </si>
+  <si>
+    <t>3.721293367020322E7</t>
+  </si>
+  <si>
+    <t>NaN</t>
+  </si>
+  <si>
+    <t>0.9545665782571059</t>
+  </si>
+  <si>
+    <t>20250714_170956</t>
+  </si>
+  <si>
+    <t>2025-07-15 11:11:47</t>
+  </si>
+  <si>
+    <t>6030.613333333334</t>
+  </si>
+  <si>
+    <t>20.102044444444445</t>
+  </si>
+  <si>
+    <t>688147117.0333334</t>
+  </si>
+  <si>
+    <t>1261154319.8296297</t>
+  </si>
+  <si>
+    <t>2597594590.8925924</t>
+  </si>
+  <si>
+    <t>1.2922041825504388E8</t>
+  </si>
+  <si>
+    <t>2.0596960657784558</t>
+  </si>
+  <si>
+    <t>6413.3189637241385</t>
+  </si>
+  <si>
+    <t>20250715_111147</t>
+  </si>
+  <si>
+    <t>2025-07-15 11:42:01</t>
+  </si>
+  <si>
+    <t>5406.123333333333</t>
+  </si>
+  <si>
+    <t>18.02041111111111</t>
+  </si>
+  <si>
+    <t>635599614.5111111</t>
+  </si>
+  <si>
+    <t>1054415467.037037</t>
+  </si>
+  <si>
+    <t>2451528101.618519</t>
+  </si>
+  <si>
+    <t>1.3604174102925676E8</t>
+  </si>
+  <si>
+    <t>2.3250115142064844</t>
+  </si>
+  <si>
+    <t>6454.137931034483</t>
+  </si>
+  <si>
+    <t>20250715_114201</t>
+  </si>
+  <si>
+    <t>2025-07-15 12:12:56</t>
+  </si>
+  <si>
+    <t>4973.0615812534015</t>
+  </si>
+  <si>
+    <t>16.57687193751134</t>
+  </si>
+  <si>
+    <t>626039193.336321</t>
+  </si>
+  <si>
+    <t>1047716397.1651958</t>
+  </si>
+  <si>
+    <t>2432706940.185407</t>
+  </si>
+  <si>
+    <t>1.4675307557154393E8</t>
+  </si>
+  <si>
+    <t>2.321913589180791</t>
+  </si>
+  <si>
+    <t>7184.507532784596</t>
+  </si>
+  <si>
+    <t>20250715_121256</t>
+  </si>
+  <si>
+    <t>2025-07-15 12:49:05</t>
+  </si>
+  <si>
+    <t>650.9066666666668</t>
+  </si>
+  <si>
+    <t>2.169688888888889</t>
+  </si>
+  <si>
+    <t>21761772.24814815</t>
+  </si>
+  <si>
+    <t>71506519.37777779</t>
+  </si>
+  <si>
+    <t>70682748.91481481</t>
+  </si>
+  <si>
+    <t>3.2577365942548513E7</t>
+  </si>
+  <si>
+    <t>0.9884797851981735</t>
+  </si>
+  <si>
+    <t>20250715_124905</t>
+  </si>
+  <si>
+    <t>2025-07-15 13:03:48</t>
+  </si>
+  <si>
+    <t>474.7633333333335</t>
+  </si>
+  <si>
+    <t>1.582544444444445</t>
+  </si>
+  <si>
+    <t>12721553.17037037</t>
+  </si>
+  <si>
+    <t>47112305.31481481</t>
+  </si>
+  <si>
+    <t>42086979.21851852</t>
+  </si>
+  <si>
+    <t>2.6594500626042906E7</t>
+  </si>
+  <si>
+    <t>0.8933330461603193</t>
+  </si>
+  <si>
+    <t>20250715_130348</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="17.45703125"/>
@@ -3142,6 +3316,324 @@
         <v>281</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>456</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>457</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>458</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>459</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>460</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>461</v>
+      </c>
+      <c r="I33" t="s" s="0">
+        <v>462</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>463</v>
+      </c>
+      <c r="K33" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="L33" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="O33" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="P33" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="Q33" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>466</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>467</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>468</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>469</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>470</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>471</v>
+      </c>
+      <c r="I34" t="s" s="0">
+        <v>472</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>463</v>
+      </c>
+      <c r="K34" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="L34" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M34" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="O34" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="P34" t="s" s="0">
+        <v>474</v>
+      </c>
+      <c r="Q34" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>476</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>477</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>478</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>479</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>480</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>481</v>
+      </c>
+      <c r="I35" t="s" s="0">
+        <v>482</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>463</v>
+      </c>
+      <c r="K35" t="s" s="0">
+        <v>483</v>
+      </c>
+      <c r="L35" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M35" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="O35" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="P35" t="s" s="0">
+        <v>484</v>
+      </c>
+      <c r="Q35" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>486</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>487</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>488</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>489</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>490</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>491</v>
+      </c>
+      <c r="I36" t="s" s="0">
+        <v>492</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>463</v>
+      </c>
+      <c r="K36" t="s" s="0">
+        <v>493</v>
+      </c>
+      <c r="L36" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="O36" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="P36" t="s" s="0">
+        <v>494</v>
+      </c>
+      <c r="Q36" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>496</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>497</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>498</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>499</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>500</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>501</v>
+      </c>
+      <c r="I37" t="s" s="0">
+        <v>502</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>463</v>
+      </c>
+      <c r="K37" t="s" s="0">
+        <v>503</v>
+      </c>
+      <c r="L37" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M37" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N37" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="O37" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="P37" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="Q37" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>505</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>506</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>507</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>508</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>509</v>
+      </c>
+      <c r="H38" t="s" s="0">
+        <v>510</v>
+      </c>
+      <c r="I38" t="s" s="0">
+        <v>511</v>
+      </c>
+      <c r="J38" t="s" s="0">
+        <v>463</v>
+      </c>
+      <c r="K38" t="s" s="0">
+        <v>512</v>
+      </c>
+      <c r="L38" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M38" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N38" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="O38" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="P38" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="Q38" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -3149,7 +3641,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F1458"/>
+  <dimension ref="A1:F1826"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="17.45703125"/>
@@ -32320,6 +32812,7366 @@
         <v>4464.26</v>
       </c>
     </row>
+    <row r="1459">
+      <c r="A1459" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1459" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1459" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1459" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1459" t="n" s="0">
+        <v>1.752505495682E9</v>
+      </c>
+      <c r="F1459" t="n" s="0">
+        <v>300.378537225</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1460" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1460" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1460" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1460" t="n" s="0">
+        <v>1.752505505682E9</v>
+      </c>
+      <c r="F1460" t="n" s="0">
+        <v>325.96112055833333</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1461" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1461" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1461" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1461" t="n" s="0">
+        <v>1.752505515682E9</v>
+      </c>
+      <c r="F1461" t="n" s="0">
+        <v>351.54370389166667</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1462" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1462" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1462" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1462" t="n" s="0">
+        <v>1.752505525682E9</v>
+      </c>
+      <c r="F1462" t="n" s="0">
+        <v>373.12913693999997</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1463" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1463" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1463" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1463" t="n" s="0">
+        <v>1.752505535682E9</v>
+      </c>
+      <c r="F1463" t="n" s="0">
+        <v>398.47533694000003</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1464" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1464" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1464" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1464" t="n" s="0">
+        <v>1.752505545682E9</v>
+      </c>
+      <c r="F1464" t="n" s="0">
+        <v>423.82153694</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1465" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1465" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1465" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1465" t="n" s="0">
+        <v>1.752505555682E9</v>
+      </c>
+      <c r="F1465" t="n" s="0">
+        <v>441.23094597</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1466" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1466" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1466" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1466" t="n" s="0">
+        <v>1.752505565682E9</v>
+      </c>
+      <c r="F1466" t="n" s="0">
+        <v>466.14571263666664</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1467" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1467" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1467" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1467" t="n" s="0">
+        <v>1.752505575682E9</v>
+      </c>
+      <c r="F1467" t="n" s="0">
+        <v>491.06047930333335</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1468" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1468" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1468" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1468" t="n" s="0">
+        <v>1.752505585682E9</v>
+      </c>
+      <c r="F1468" t="n" s="0">
+        <v>509.0785100571428</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1469" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1469" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1469" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1469" t="n" s="0">
+        <v>1.752505595682E9</v>
+      </c>
+      <c r="F1469" t="n" s="0">
+        <v>533.6773671999999</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1470" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1470" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1470" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1470" t="n" s="0">
+        <v>1.752505605682E9</v>
+      </c>
+      <c r="F1470" t="n" s="0">
+        <v>558.2762243428572</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1471" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1471" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1471" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1471" t="n" s="0">
+        <v>1.752505615682E9</v>
+      </c>
+      <c r="F1471" t="n" s="0">
+        <v>573.7891117125</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1472" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1472" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1472" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1472" t="n" s="0">
+        <v>1.752505625682E9</v>
+      </c>
+      <c r="F1472" t="n" s="0">
+        <v>598.0053081410714</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1473" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1473" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1473" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1473" t="n" s="0">
+        <v>1.752505635682E9</v>
+      </c>
+      <c r="F1473" t="n" s="0">
+        <v>622.2215045696429</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1474" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1474" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1474" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1474" t="n" s="0">
+        <v>1.752505645682E9</v>
+      </c>
+      <c r="F1474" t="n" s="0">
+        <v>641.9068923125001</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1475" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1475" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1475" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1475" t="n" s="0">
+        <v>1.752505655682E9</v>
+      </c>
+      <c r="F1475" t="n" s="0">
+        <v>662.7464062013888</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1476" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1476" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1476" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1476" t="n" s="0">
+        <v>1.752505665682E9</v>
+      </c>
+      <c r="F1476" t="n" s="0">
+        <v>683.5859200902778</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1477" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1477" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1477" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1477" t="n" s="0">
+        <v>1.752505675682E9</v>
+      </c>
+      <c r="F1477" t="n" s="0">
+        <v>682.7766666666666</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1478" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1478" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1478" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1478" t="n" s="0">
+        <v>1.752505685682E9</v>
+      </c>
+      <c r="F1478" t="n" s="0">
+        <v>682.7766666666666</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1479" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1479" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1479" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1479" t="n" s="0">
+        <v>1.752505695682E9</v>
+      </c>
+      <c r="F1479" t="n" s="0">
+        <v>682.7766666666666</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1480" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1480" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1480" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1480" t="n" s="0">
+        <v>1.752505705682E9</v>
+      </c>
+      <c r="F1480" t="n" s="0">
+        <v>671.79</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1481" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1481" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1481" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1481" t="n" s="0">
+        <v>1.752505715682E9</v>
+      </c>
+      <c r="F1481" t="n" s="0">
+        <v>671.79</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1482" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1482" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1482" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1482" t="n" s="0">
+        <v>1.752505725682E9</v>
+      </c>
+      <c r="F1482" t="n" s="0">
+        <v>671.79</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1483" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1483" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1483" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1483" t="n" s="0">
+        <v>1.752505735682E9</v>
+      </c>
+      <c r="F1483" t="n" s="0">
+        <v>672.2733333333333</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1484" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1484" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1484" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1484" t="n" s="0">
+        <v>1.752505745682E9</v>
+      </c>
+      <c r="F1484" t="n" s="0">
+        <v>672.2733333333333</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1485" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1485" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1485" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1485" t="n" s="0">
+        <v>1.752505755682E9</v>
+      </c>
+      <c r="F1485" t="n" s="0">
+        <v>672.2733333333333</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1486" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1486" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1486" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1486" t="n" s="0">
+        <v>1.752505765682E9</v>
+      </c>
+      <c r="F1486" t="n" s="0">
+        <v>661.3833333333333</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1487" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1487" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1487" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1487" t="n" s="0">
+        <v>1.752505775682E9</v>
+      </c>
+      <c r="F1487" t="n" s="0">
+        <v>661.3833333333333</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1488" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1488" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1488" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1488" t="n" s="0">
+        <v>1.752505785682E9</v>
+      </c>
+      <c r="F1488" t="n" s="0">
+        <v>661.3833333333333</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1489" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1489" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1489" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1489" t="n" s="0">
+        <v>1.752505795682E9</v>
+      </c>
+      <c r="F1489" t="n" s="0">
+        <v>645.69</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1490" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1490" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1490" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1490" t="n" s="0">
+        <v>1.752505495682E9</v>
+      </c>
+      <c r="F1490" t="n" s="0">
+        <v>132.6819767</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1491" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1491" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1491" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1491" t="n" s="0">
+        <v>1.752505505682E9</v>
+      </c>
+      <c r="F1491" t="n" s="0">
+        <v>131.5729767</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1492" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1492" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1492" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1492" t="n" s="0">
+        <v>1.752505515682E9</v>
+      </c>
+      <c r="F1492" t="n" s="0">
+        <v>130.4639767</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1493" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1493" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1493" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1493" t="n" s="0">
+        <v>1.752505525682E9</v>
+      </c>
+      <c r="F1493" t="n" s="0">
+        <v>214.50666666666666</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1494" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1494" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1494" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1494" t="n" s="0">
+        <v>1.752505535682E9</v>
+      </c>
+      <c r="F1494" t="n" s="0">
+        <v>214.50666666666666</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1495" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1495" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1495" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1495" t="n" s="0">
+        <v>1.752505545682E9</v>
+      </c>
+      <c r="F1495" t="n" s="0">
+        <v>214.50666666666666</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1496" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1496" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1496" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1496" t="n" s="0">
+        <v>1.752505555682E9</v>
+      </c>
+      <c r="F1496" t="n" s="0">
+        <v>294.91</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1497" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1497" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1497" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1497" t="n" s="0">
+        <v>1.752505565682E9</v>
+      </c>
+      <c r="F1497" t="n" s="0">
+        <v>294.91</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1498" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1498" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1498" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1498" t="n" s="0">
+        <v>1.752505575682E9</v>
+      </c>
+      <c r="F1498" t="n" s="0">
+        <v>294.91</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1499" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1499" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1499" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1499" t="n" s="0">
+        <v>1.752505585682E9</v>
+      </c>
+      <c r="F1499" t="n" s="0">
+        <v>349.68333333333334</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1500" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1500" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1500" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1500" t="n" s="0">
+        <v>1.752505595682E9</v>
+      </c>
+      <c r="F1500" t="n" s="0">
+        <v>349.68333333333334</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1501" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1501" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1501" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1501" t="n" s="0">
+        <v>1.752505605682E9</v>
+      </c>
+      <c r="F1501" t="n" s="0">
+        <v>349.68333333333334</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1502" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1502" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1502" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1502" t="n" s="0">
+        <v>1.752505615682E9</v>
+      </c>
+      <c r="F1502" t="n" s="0">
+        <v>416.54999999999995</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1503" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1503" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1503" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1503" t="n" s="0">
+        <v>1.752505625682E9</v>
+      </c>
+      <c r="F1503" t="n" s="0">
+        <v>416.54999999999995</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1504" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1504" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1504" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1504" t="n" s="0">
+        <v>1.752505635682E9</v>
+      </c>
+      <c r="F1504" t="n" s="0">
+        <v>416.54999999999995</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1505" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1505" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1505" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1505" t="n" s="0">
+        <v>1.752505645682E9</v>
+      </c>
+      <c r="F1505" t="n" s="0">
+        <v>452.48</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1506" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1506" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1506" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1506" t="n" s="0">
+        <v>1.752505655682E9</v>
+      </c>
+      <c r="F1506" t="n" s="0">
+        <v>452.48</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1507" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1507" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1507" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1507" t="n" s="0">
+        <v>1.752505665682E9</v>
+      </c>
+      <c r="F1507" t="n" s="0">
+        <v>452.48</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1508" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1508" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1508" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1508" t="n" s="0">
+        <v>1.752505675682E9</v>
+      </c>
+      <c r="F1508" t="n" s="0">
+        <v>494.7966666666667</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1509" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1509" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1509" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1509" t="n" s="0">
+        <v>1.752505685682E9</v>
+      </c>
+      <c r="F1509" t="n" s="0">
+        <v>494.7966666666667</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1510" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1510" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1510" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1510" t="n" s="0">
+        <v>1.752505695682E9</v>
+      </c>
+      <c r="F1510" t="n" s="0">
+        <v>494.7966666666667</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1511" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1511" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1511" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1511" t="n" s="0">
+        <v>1.752505705682E9</v>
+      </c>
+      <c r="F1511" t="n" s="0">
+        <v>543.5647203000001</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1512" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1512" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1512" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1512" t="n" s="0">
+        <v>1.752505715682E9</v>
+      </c>
+      <c r="F1512" t="n" s="0">
+        <v>545.9100000000001</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1513" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1513" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1513" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1513" t="n" s="0">
+        <v>1.752505725682E9</v>
+      </c>
+      <c r="F1513" t="n" s="0">
+        <v>545.9100000000001</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1514" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1514" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1514" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1514" t="n" s="0">
+        <v>1.752505735682E9</v>
+      </c>
+      <c r="F1514" t="n" s="0">
+        <v>593.5077307333333</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1515" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1515" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1515" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1515" t="n" s="0">
+        <v>1.752505745682E9</v>
+      </c>
+      <c r="F1515" t="n" s="0">
+        <v>598.8733333333333</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1516" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1516" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1516" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1516" t="n" s="0">
+        <v>1.752505755682E9</v>
+      </c>
+      <c r="F1516" t="n" s="0">
+        <v>598.8733333333333</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1517" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1517" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1517" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1517" t="n" s="0">
+        <v>1.752505765682E9</v>
+      </c>
+      <c r="F1517" t="n" s="0">
+        <v>617.7881434</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1518" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1518" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1518" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1518" t="n" s="0">
+        <v>1.752505775682E9</v>
+      </c>
+      <c r="F1518" t="n" s="0">
+        <v>623.7700000000001</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1519" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1519" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1519" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1519" t="n" s="0">
+        <v>1.752505785682E9</v>
+      </c>
+      <c r="F1519" t="n" s="0">
+        <v>623.7700000000001</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B1520" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1520" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="D1520" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1520" t="n" s="0">
+        <v>1.752505795682E9</v>
+      </c>
+      <c r="F1520" t="n" s="0">
+        <v>569.2933333333333</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1521" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1521" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1521" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1521" t="n" s="0">
+        <v>1.752570406605E9</v>
+      </c>
+      <c r="F1521" t="n" s="0">
+        <v>112.78103300000001</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1522" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1522" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1522" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1522" t="n" s="0">
+        <v>1.752570416605E9</v>
+      </c>
+      <c r="F1522" t="n" s="0">
+        <v>120.25503300000001</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1523" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1523" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1523" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1523" t="n" s="0">
+        <v>1.752570426605E9</v>
+      </c>
+      <c r="F1523" t="n" s="0">
+        <v>116.98517279999999</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1524" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1524" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1524" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1524" t="n" s="0">
+        <v>1.752570436605E9</v>
+      </c>
+      <c r="F1524" t="n" s="0">
+        <v>123.80357279999998</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1525" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1525" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1525" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1525" t="n" s="0">
+        <v>1.752570446605E9</v>
+      </c>
+      <c r="F1525" t="n" s="0">
+        <v>130.62197279999998</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1526" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1526" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1526" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1526" t="n" s="0">
+        <v>1.752570456605E9</v>
+      </c>
+      <c r="F1526" t="n" s="0">
+        <v>127.07226699999997</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1527" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1527" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1527" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1527" t="n" s="0">
+        <v>1.752570466605E9</v>
+      </c>
+      <c r="F1527" t="n" s="0">
+        <v>133.37326699999997</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1528" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1528" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1528" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1528" t="n" s="0">
+        <v>1.752570476605E9</v>
+      </c>
+      <c r="F1528" t="n" s="0">
+        <v>139.67426699999996</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1529" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1529" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1529" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1529" t="n" s="0">
+        <v>1.752570486605E9</v>
+      </c>
+      <c r="F1529" t="n" s="0">
+        <v>136.84415942857146</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1530" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1530" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1530" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1530" t="n" s="0">
+        <v>1.752570496605E9</v>
+      </c>
+      <c r="F1530" t="n" s="0">
+        <v>142.75101657142864</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1531" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1531" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1531" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1531" t="n" s="0">
+        <v>1.752570506605E9</v>
+      </c>
+      <c r="F1531" t="n" s="0">
+        <v>148.65787371428576</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1532" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1532" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1532" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1532" t="n" s="0">
+        <v>1.752570516605E9</v>
+      </c>
+      <c r="F1532" t="n" s="0">
+        <v>146.98658074999997</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1533" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1533" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1533" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1533" t="n" s="0">
+        <v>1.752570526605E9</v>
+      </c>
+      <c r="F1533" t="n" s="0">
+        <v>152.60383075</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1534" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1534" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1534" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1534" t="n" s="0">
+        <v>1.752570536605E9</v>
+      </c>
+      <c r="F1534" t="n" s="0">
+        <v>158.22108075</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1535" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1535" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1535" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1535" t="n" s="0">
+        <v>1.752570546605E9</v>
+      </c>
+      <c r="F1535" t="n" s="0">
+        <v>157.144234</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1536" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1536" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1536" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1536" t="n" s="0">
+        <v>1.752570556605E9</v>
+      </c>
+      <c r="F1536" t="n" s="0">
+        <v>158.72666666666666</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1537" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1537" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1537" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1537" t="n" s="0">
+        <v>1.752570566605E9</v>
+      </c>
+      <c r="F1537" t="n" s="0">
+        <v>158.72666666666666</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1538" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1538" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1538" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1538" t="n" s="0">
+        <v>1.752570576605E9</v>
+      </c>
+      <c r="F1538" t="n" s="0">
+        <v>145.12666666666667</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1539" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1539" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1539" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1539" t="n" s="0">
+        <v>1.752570586605E9</v>
+      </c>
+      <c r="F1539" t="n" s="0">
+        <v>145.12666666666667</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1540" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1540" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1540" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1540" t="n" s="0">
+        <v>1.752570596605E9</v>
+      </c>
+      <c r="F1540" t="n" s="0">
+        <v>145.12666666666667</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1541" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1541" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1541" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1541" t="n" s="0">
+        <v>1.752570606605E9</v>
+      </c>
+      <c r="F1541" t="n" s="0">
+        <v>129.8233333333333</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1542" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1542" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1542" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1542" t="n" s="0">
+        <v>1.752570616605E9</v>
+      </c>
+      <c r="F1542" t="n" s="0">
+        <v>129.8233333333333</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1543" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1543" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1543" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1543" t="n" s="0">
+        <v>1.752570626605E9</v>
+      </c>
+      <c r="F1543" t="n" s="0">
+        <v>129.8233333333333</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1544" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1544" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1544" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1544" t="n" s="0">
+        <v>1.752570636605E9</v>
+      </c>
+      <c r="F1544" t="n" s="0">
+        <v>117.17666666666668</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1545" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1545" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1545" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1545" t="n" s="0">
+        <v>1.752570646605E9</v>
+      </c>
+      <c r="F1545" t="n" s="0">
+        <v>117.17666666666668</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1546" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1546" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1546" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1546" t="n" s="0">
+        <v>1.752570656605E9</v>
+      </c>
+      <c r="F1546" t="n" s="0">
+        <v>117.17666666666668</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1547" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1547" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1547" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1547" t="n" s="0">
+        <v>1.752570666605E9</v>
+      </c>
+      <c r="F1547" t="n" s="0">
+        <v>103.78666666666669</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1548" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1548" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1548" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1548" t="n" s="0">
+        <v>1.752570676605E9</v>
+      </c>
+      <c r="F1548" t="n" s="0">
+        <v>103.78666666666669</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1549" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1549" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1549" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1549" t="n" s="0">
+        <v>1.752570686605E9</v>
+      </c>
+      <c r="F1549" t="n" s="0">
+        <v>103.78666666666669</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1550" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1550" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1550" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1550" t="n" s="0">
+        <v>1.752570696605E9</v>
+      </c>
+      <c r="F1550" t="n" s="0">
+        <v>100.25666666666665</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1551" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1551" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1551" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1551" t="n" s="0">
+        <v>1.752570706605E9</v>
+      </c>
+      <c r="F1551" t="n" s="0">
+        <v>100.25666666666665</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1552" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1552" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1552" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1552" t="n" s="0">
+        <v>1.752570406605E9</v>
+      </c>
+      <c r="F1552" t="n" s="0">
+        <v>832.5432020000001</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1553" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1553" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1553" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1553" t="n" s="0">
+        <v>1.752570416605E9</v>
+      </c>
+      <c r="F1553" t="n" s="0">
+        <v>841.3992020000001</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1554" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1554" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1554" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1554" t="n" s="0">
+        <v>1.752570426605E9</v>
+      </c>
+      <c r="F1554" t="n" s="0">
+        <v>1339.3787945333333</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1555" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1555" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1555" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1555" t="n" s="0">
+        <v>1.752570436605E9</v>
+      </c>
+      <c r="F1555" t="n" s="0">
+        <v>1350.2290612</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1556" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1556" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1556" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1556" t="n" s="0">
+        <v>1.752570446605E9</v>
+      </c>
+      <c r="F1556" t="n" s="0">
+        <v>1361.0793278666665</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1557" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1557" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1557" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1557" t="n" s="0">
+        <v>1.752570456605E9</v>
+      </c>
+      <c r="F1557" t="n" s="0">
+        <v>2201.2108959444445</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1558" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1558" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1558" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1558" t="n" s="0">
+        <v>1.752570466605E9</v>
+      </c>
+      <c r="F1558" t="n" s="0">
+        <v>2228.4659118333334</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1559" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1559" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1559" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1559" t="n" s="0">
+        <v>1.752570476605E9</v>
+      </c>
+      <c r="F1559" t="n" s="0">
+        <v>2240.451411833333</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1560" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1560" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1560" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1560" t="n" s="0">
+        <v>1.752570486605E9</v>
+      </c>
+      <c r="F1560" t="n" s="0">
+        <v>2504.436305047619</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1561" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1561" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1561" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1561" t="n" s="0">
+        <v>1.752570496605E9</v>
+      </c>
+      <c r="F1561" t="n" s="0">
+        <v>2522.6371621904764</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1562" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1562" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1562" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1562" t="n" s="0">
+        <v>1.752570506605E9</v>
+      </c>
+      <c r="F1562" t="n" s="0">
+        <v>2540.8380193333332</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1563" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1563" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1563" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1563" t="n" s="0">
+        <v>1.752570516605E9</v>
+      </c>
+      <c r="F1563" t="n" s="0">
+        <v>3170.5773136666667</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1564" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1564" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1564" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1564" t="n" s="0">
+        <v>1.752570526605E9</v>
+      </c>
+      <c r="F1564" t="n" s="0">
+        <v>3191.518313666667</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1565" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1565" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1565" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1565" t="n" s="0">
+        <v>1.752570536605E9</v>
+      </c>
+      <c r="F1565" t="n" s="0">
+        <v>3212.4593136666667</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1566" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1566" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1566" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1566" t="n" s="0">
+        <v>1.752570546605E9</v>
+      </c>
+      <c r="F1566" t="n" s="0">
+        <v>3798.6553591111115</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1567" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1567" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1567" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1567" t="n" s="0">
+        <v>1.752570556605E9</v>
+      </c>
+      <c r="F1567" t="n" s="0">
+        <v>3820.1771368888894</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1568" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1568" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1568" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1568" t="n" s="0">
+        <v>1.752570566605E9</v>
+      </c>
+      <c r="F1568" t="n" s="0">
+        <v>3837.696666666667</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1569" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1569" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1569" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1569" t="n" s="0">
+        <v>1.752570576605E9</v>
+      </c>
+      <c r="F1569" t="n" s="0">
+        <v>4408.251504777778</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1570" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1570" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1570" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1570" t="n" s="0">
+        <v>1.752570586605E9</v>
+      </c>
+      <c r="F1570" t="n" s="0">
+        <v>4422.543615888889</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1571" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1571" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1571" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1571" t="n" s="0">
+        <v>1.752570596605E9</v>
+      </c>
+      <c r="F1571" t="n" s="0">
+        <v>4430.150000000001</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1572" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1572" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1572" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1572" t="n" s="0">
+        <v>1.752570606605E9</v>
+      </c>
+      <c r="F1572" t="n" s="0">
+        <v>4987.033944333333</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1573" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1573" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1573" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1573" t="n" s="0">
+        <v>1.752570616605E9</v>
+      </c>
+      <c r="F1573" t="n" s="0">
+        <v>5001.65</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1574" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1574" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1574" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1574" t="n" s="0">
+        <v>1.752570626605E9</v>
+      </c>
+      <c r="F1574" t="n" s="0">
+        <v>5001.65</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1575" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1575" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1575" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1575" t="n" s="0">
+        <v>1.752570636605E9</v>
+      </c>
+      <c r="F1575" t="n" s="0">
+        <v>5493.076548777778</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1576" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1576" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1576" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1576" t="n" s="0">
+        <v>1.752570646605E9</v>
+      </c>
+      <c r="F1576" t="n" s="0">
+        <v>5508.8133333333335</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1577" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1577" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1577" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1577" t="n" s="0">
+        <v>1.752570656605E9</v>
+      </c>
+      <c r="F1577" t="n" s="0">
+        <v>5508.8133333333335</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1578" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1578" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1578" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1578" t="n" s="0">
+        <v>1.752570666605E9</v>
+      </c>
+      <c r="F1578" t="n" s="0">
+        <v>6003.727315666667</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1579" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1579" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1579" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1579" t="n" s="0">
+        <v>1.752570676605E9</v>
+      </c>
+      <c r="F1579" t="n" s="0">
+        <v>6019.126666666667</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1580" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1580" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1580" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1580" t="n" s="0">
+        <v>1.752570686605E9</v>
+      </c>
+      <c r="F1580" t="n" s="0">
+        <v>6019.126666666667</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1581" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1581" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1581" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1581" t="n" s="0">
+        <v>1.752570696605E9</v>
+      </c>
+      <c r="F1581" t="n" s="0">
+        <v>6030.613333333334</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1582" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1582" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="D1582" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1582" t="n" s="0">
+        <v>1.752570706605E9</v>
+      </c>
+      <c r="F1582" t="n" s="0">
+        <v>6030.613333333334</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1583" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1583" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1583" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1583" t="n" s="0">
+        <v>1.752572221549E9</v>
+      </c>
+      <c r="F1583" t="n" s="0">
+        <v>190.12666666666672</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1584" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1584" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1584" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1584" t="n" s="0">
+        <v>1.752572231549E9</v>
+      </c>
+      <c r="F1584" t="n" s="0">
+        <v>190.12666666666672</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1585" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1585" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1585" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1585" t="n" s="0">
+        <v>1.752572241549E9</v>
+      </c>
+      <c r="F1585" t="n" s="0">
+        <v>190.12666666666672</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1586" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1586" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1586" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1586" t="n" s="0">
+        <v>1.752572251549E9</v>
+      </c>
+      <c r="F1586" t="n" s="0">
+        <v>180.02000000000004</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1587" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1587" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1587" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1587" t="n" s="0">
+        <v>1.752572261549E9</v>
+      </c>
+      <c r="F1587" t="n" s="0">
+        <v>180.02000000000004</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1588" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1588" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1588" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1588" t="n" s="0">
+        <v>1.752572271549E9</v>
+      </c>
+      <c r="F1588" t="n" s="0">
+        <v>180.02000000000004</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1589" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1589" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1589" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1589" t="n" s="0">
+        <v>1.752572281549E9</v>
+      </c>
+      <c r="F1589" t="n" s="0">
+        <v>170.30333333333337</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1590" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1590" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1590" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1590" t="n" s="0">
+        <v>1.752572291549E9</v>
+      </c>
+      <c r="F1590" t="n" s="0">
+        <v>170.30333333333337</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1591" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1591" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1591" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1591" t="n" s="0">
+        <v>1.752572301549E9</v>
+      </c>
+      <c r="F1591" t="n" s="0">
+        <v>170.30333333333337</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1592" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1592" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1592" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1592" t="n" s="0">
+        <v>1.752572311549E9</v>
+      </c>
+      <c r="F1592" t="n" s="0">
+        <v>160.6566666666667</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1593" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1593" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1593" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1593" t="n" s="0">
+        <v>1.752572321549E9</v>
+      </c>
+      <c r="F1593" t="n" s="0">
+        <v>160.6566666666667</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1594" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1594" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1594" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1594" t="n" s="0">
+        <v>1.752572331549E9</v>
+      </c>
+      <c r="F1594" t="n" s="0">
+        <v>160.6566666666667</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1595" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1595" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1595" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1595" t="n" s="0">
+        <v>1.752572341549E9</v>
+      </c>
+      <c r="F1595" t="n" s="0">
+        <v>150.06333333333336</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1596" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1596" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1596" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1596" t="n" s="0">
+        <v>1.752572351549E9</v>
+      </c>
+      <c r="F1596" t="n" s="0">
+        <v>150.06333333333336</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1597" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1597" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1597" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1597" t="n" s="0">
+        <v>1.752572361549E9</v>
+      </c>
+      <c r="F1597" t="n" s="0">
+        <v>150.06333333333336</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1598" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1598" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1598" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1598" t="n" s="0">
+        <v>1.752572371549E9</v>
+      </c>
+      <c r="F1598" t="n" s="0">
+        <v>141.14666666666673</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1599" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1599" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1599" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1599" t="n" s="0">
+        <v>1.752572381549E9</v>
+      </c>
+      <c r="F1599" t="n" s="0">
+        <v>141.14666666666673</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1600" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1600" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1600" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1600" t="n" s="0">
+        <v>1.752572391549E9</v>
+      </c>
+      <c r="F1600" t="n" s="0">
+        <v>141.14666666666673</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1601" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1601" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1601" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1601" t="n" s="0">
+        <v>1.752572401549E9</v>
+      </c>
+      <c r="F1601" t="n" s="0">
+        <v>132.35000000000002</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1602" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1602" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1602" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1602" t="n" s="0">
+        <v>1.752572411549E9</v>
+      </c>
+      <c r="F1602" t="n" s="0">
+        <v>132.35000000000002</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1603" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1603" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1603" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1603" t="n" s="0">
+        <v>1.752572421549E9</v>
+      </c>
+      <c r="F1603" t="n" s="0">
+        <v>132.35000000000002</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1604" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1604" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1604" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1604" t="n" s="0">
+        <v>1.752572431549E9</v>
+      </c>
+      <c r="F1604" t="n" s="0">
+        <v>124.98333333333335</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1605" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1605" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1605" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1605" t="n" s="0">
+        <v>1.752572441549E9</v>
+      </c>
+      <c r="F1605" t="n" s="0">
+        <v>124.98333333333335</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1606" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1606" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1606" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1606" t="n" s="0">
+        <v>1.752572451549E9</v>
+      </c>
+      <c r="F1606" t="n" s="0">
+        <v>124.98333333333335</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1607" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1607" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1607" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1607" t="n" s="0">
+        <v>1.752572461549E9</v>
+      </c>
+      <c r="F1607" t="n" s="0">
+        <v>118.84999999999991</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1608" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1608" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1608" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1608" t="n" s="0">
+        <v>1.752572471549E9</v>
+      </c>
+      <c r="F1608" t="n" s="0">
+        <v>118.84999999999991</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1609" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1609" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1609" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1609" t="n" s="0">
+        <v>1.752572481549E9</v>
+      </c>
+      <c r="F1609" t="n" s="0">
+        <v>118.84999999999991</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1610" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1610" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1610" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1610" t="n" s="0">
+        <v>1.752572491549E9</v>
+      </c>
+      <c r="F1610" t="n" s="0">
+        <v>116.76999999999995</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1611" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1611" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1611" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1611" t="n" s="0">
+        <v>1.752572501549E9</v>
+      </c>
+      <c r="F1611" t="n" s="0">
+        <v>116.76999999999995</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1612" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1612" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1612" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1612" t="n" s="0">
+        <v>1.752572511549E9</v>
+      </c>
+      <c r="F1612" t="n" s="0">
+        <v>116.76999999999995</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1613" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1613" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1613" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1613" t="n" s="0">
+        <v>1.752572521549E9</v>
+      </c>
+      <c r="F1613" t="n" s="0">
+        <v>118.76666666666654</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1614" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1614" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1614" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1614" t="n" s="0">
+        <v>1.752572221549E9</v>
+      </c>
+      <c r="F1614" t="n" s="0">
+        <v>512.5900000000003</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1615" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1615" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1615" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1615" t="n" s="0">
+        <v>1.752572231549E9</v>
+      </c>
+      <c r="F1615" t="n" s="0">
+        <v>512.5900000000003</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1616" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1616" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1616" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1616" t="n" s="0">
+        <v>1.752572241549E9</v>
+      </c>
+      <c r="F1616" t="n" s="0">
+        <v>512.5900000000003</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1617" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1617" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1617" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1617" t="n" s="0">
+        <v>1.752572251549E9</v>
+      </c>
+      <c r="F1617" t="n" s="0">
+        <v>907.5533333333336</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1618" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1618" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1618" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1618" t="n" s="0">
+        <v>1.752572261549E9</v>
+      </c>
+      <c r="F1618" t="n" s="0">
+        <v>907.5533333333336</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1619" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1619" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1619" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1619" t="n" s="0">
+        <v>1.752572271549E9</v>
+      </c>
+      <c r="F1619" t="n" s="0">
+        <v>907.5533333333336</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1620" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1620" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1620" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1620" t="n" s="0">
+        <v>1.752572281549E9</v>
+      </c>
+      <c r="F1620" t="n" s="0">
+        <v>1560.6233333333334</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1621" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1621" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1621" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1621" t="n" s="0">
+        <v>1.752572291549E9</v>
+      </c>
+      <c r="F1621" t="n" s="0">
+        <v>1560.6233333333334</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1622" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1622" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1622" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1622" t="n" s="0">
+        <v>1.752572301549E9</v>
+      </c>
+      <c r="F1622" t="n" s="0">
+        <v>1560.6233333333334</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1623" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1623" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1623" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1623" t="n" s="0">
+        <v>1.752572311549E9</v>
+      </c>
+      <c r="F1623" t="n" s="0">
+        <v>2133.76</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1624" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1624" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1624" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1624" t="n" s="0">
+        <v>1.752572321549E9</v>
+      </c>
+      <c r="F1624" t="n" s="0">
+        <v>2133.76</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1625" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1625" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1625" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1625" t="n" s="0">
+        <v>1.752572331549E9</v>
+      </c>
+      <c r="F1625" t="n" s="0">
+        <v>2133.76</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1626" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1626" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1626" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1626" t="n" s="0">
+        <v>1.752572341549E9</v>
+      </c>
+      <c r="F1626" t="n" s="0">
+        <v>2648.206666666667</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1627" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1627" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1627" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1627" t="n" s="0">
+        <v>1.752572351549E9</v>
+      </c>
+      <c r="F1627" t="n" s="0">
+        <v>2648.206666666667</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1628" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1628" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1628" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1628" t="n" s="0">
+        <v>1.752572361549E9</v>
+      </c>
+      <c r="F1628" t="n" s="0">
+        <v>2648.206666666667</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1629" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1629" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1629" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1629" t="n" s="0">
+        <v>1.752572371549E9</v>
+      </c>
+      <c r="F1629" t="n" s="0">
+        <v>3148.183333333334</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1630" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1630" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1630" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1630" t="n" s="0">
+        <v>1.752572381549E9</v>
+      </c>
+      <c r="F1630" t="n" s="0">
+        <v>3148.183333333334</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1631" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1631" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1631" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1631" t="n" s="0">
+        <v>1.752572391549E9</v>
+      </c>
+      <c r="F1631" t="n" s="0">
+        <v>3148.183333333334</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1632" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1632" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1632" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1632" t="n" s="0">
+        <v>1.752572401549E9</v>
+      </c>
+      <c r="F1632" t="n" s="0">
+        <v>3665.106666666667</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1633" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1633" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1633" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1633" t="n" s="0">
+        <v>1.752572411549E9</v>
+      </c>
+      <c r="F1633" t="n" s="0">
+        <v>3665.106666666667</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1634" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1634" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1634" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1634" t="n" s="0">
+        <v>1.752572421549E9</v>
+      </c>
+      <c r="F1634" t="n" s="0">
+        <v>3665.106666666667</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1635" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1635" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1635" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1635" t="n" s="0">
+        <v>1.752572431549E9</v>
+      </c>
+      <c r="F1635" t="n" s="0">
+        <v>4271.223333333333</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1636" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1636" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1636" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1636" t="n" s="0">
+        <v>1.752572441549E9</v>
+      </c>
+      <c r="F1636" t="n" s="0">
+        <v>4271.223333333333</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1637" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1637" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1637" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1637" t="n" s="0">
+        <v>1.752572451549E9</v>
+      </c>
+      <c r="F1637" t="n" s="0">
+        <v>4271.223333333333</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1638" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1638" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1638" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1638" t="n" s="0">
+        <v>1.752572461549E9</v>
+      </c>
+      <c r="F1638" t="n" s="0">
+        <v>4783.666666666668</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1639" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1639" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1639" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1639" t="n" s="0">
+        <v>1.752572471549E9</v>
+      </c>
+      <c r="F1639" t="n" s="0">
+        <v>4783.666666666668</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1640" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1640" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1640" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1640" t="n" s="0">
+        <v>1.752572481549E9</v>
+      </c>
+      <c r="F1640" t="n" s="0">
+        <v>4783.666666666668</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1641" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1641" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1641" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1641" t="n" s="0">
+        <v>1.752572491549E9</v>
+      </c>
+      <c r="F1641" t="n" s="0">
+        <v>5284.8133333333335</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1642" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1642" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1642" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1642" t="n" s="0">
+        <v>1.752572501549E9</v>
+      </c>
+      <c r="F1642" t="n" s="0">
+        <v>5284.8133333333335</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1643" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1643" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1643" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1643" t="n" s="0">
+        <v>1.752572511549E9</v>
+      </c>
+      <c r="F1643" t="n" s="0">
+        <v>5284.8133333333335</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1644" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1644" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="D1644" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1644" t="n" s="0">
+        <v>1.752572521549E9</v>
+      </c>
+      <c r="F1644" t="n" s="0">
+        <v>5406.123333333333</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1645" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1645" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1645" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1645" t="n" s="0">
+        <v>1.752574096342E9</v>
+      </c>
+      <c r="F1645" t="n" s="0">
+        <v>19.36576199999987</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1646" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1646" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1646" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1646" t="n" s="0">
+        <v>1.752574106342E9</v>
+      </c>
+      <c r="F1646" t="n" s="0">
+        <v>23.39576199999984</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1647" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1647" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1647" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1647" t="n" s="0">
+        <v>1.752574116342E9</v>
+      </c>
+      <c r="F1647" t="n" s="0">
+        <v>27.425761999999818</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1648" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1648" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1648" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1648" t="n" s="0">
+        <v>1.752574126342E9</v>
+      </c>
+      <c r="F1648" t="n" s="0">
+        <v>30.64009769999955</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1649" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1649" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1649" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1649" t="n" s="0">
+        <v>1.752574136342E9</v>
+      </c>
+      <c r="F1649" t="n" s="0">
+        <v>34.56559769999949</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1650" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1650" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1650" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1650" t="n" s="0">
+        <v>1.752574146342E9</v>
+      </c>
+      <c r="F1650" t="n" s="0">
+        <v>38.49109769999944</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1651" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1651" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1651" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1651" t="n" s="0">
+        <v>1.752574156342E9</v>
+      </c>
+      <c r="F1651" t="n" s="0">
+        <v>44.2229003999998</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1652" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1652" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1652" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1652" t="n" s="0">
+        <v>1.752574166342E9</v>
+      </c>
+      <c r="F1652" t="n" s="0">
+        <v>48.315567066666446</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1653" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1653" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1653" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1653" t="n" s="0">
+        <v>1.752574176342E9</v>
+      </c>
+      <c r="F1653" t="n" s="0">
+        <v>52.40823373333309</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1654" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1654" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1654" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1654" t="n" s="0">
+        <v>1.752574186342E9</v>
+      </c>
+      <c r="F1654" t="n" s="0">
+        <v>54.275526947691965</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1655" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1655" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1655" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1655" t="n" s="0">
+        <v>1.752574196342E9</v>
+      </c>
+      <c r="F1655" t="n" s="0">
+        <v>58.20699418546497</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1656" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1656" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1656" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1656" t="n" s="0">
+        <v>1.752574206342E9</v>
+      </c>
+      <c r="F1656" t="n" s="0">
+        <v>62.138461423237985</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1657" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1657" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1657" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1657" t="n" s="0">
+        <v>1.752574216342E9</v>
+      </c>
+      <c r="F1657" t="n" s="0">
+        <v>62.47911612000006</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1658" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1658" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1658" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1658" t="n" s="0">
+        <v>1.752574226342E9</v>
+      </c>
+      <c r="F1658" t="n" s="0">
+        <v>66.19691612000005</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1659" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1659" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1659" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1659" t="n" s="0">
+        <v>1.752574236342E9</v>
+      </c>
+      <c r="F1659" t="n" s="0">
+        <v>69.91471612000007</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1660" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1660" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1660" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1660" t="n" s="0">
+        <v>1.752574246342E9</v>
+      </c>
+      <c r="F1660" t="n" s="0">
+        <v>71.93944520585978</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1661" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1661" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1661" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1661" t="n" s="0">
+        <v>1.752574256342E9</v>
+      </c>
+      <c r="F1661" t="n" s="0">
+        <v>75.57175835967558</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1662" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1662" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1662" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1662" t="n" s="0">
+        <v>1.752574266342E9</v>
+      </c>
+      <c r="F1662" t="n" s="0">
+        <v>79.20407151349139</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1663" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1663" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1663" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1663" t="n" s="0">
+        <v>1.752574276342E9</v>
+      </c>
+      <c r="F1663" t="n" s="0">
+        <v>82.69852832809619</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1664" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1664" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1664" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1664" t="n" s="0">
+        <v>1.752574286342E9</v>
+      </c>
+      <c r="F1664" t="n" s="0">
+        <v>86.32479677443692</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1665" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1665" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1665" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1665" t="n" s="0">
+        <v>1.752574296342E9</v>
+      </c>
+      <c r="F1665" t="n" s="0">
+        <v>89.95106522077764</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1666" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1666" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1666" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1666" t="n" s="0">
+        <v>1.752574306342E9</v>
+      </c>
+      <c r="F1666" t="n" s="0">
+        <v>92.01883072499989</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1667" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1667" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1667" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1667" t="n" s="0">
+        <v>1.752574316342E9</v>
+      </c>
+      <c r="F1667" t="n" s="0">
+        <v>95.58470572499988</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1668" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1668" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1668" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1668" t="n" s="0">
+        <v>1.752574326342E9</v>
+      </c>
+      <c r="F1668" t="n" s="0">
+        <v>99.15058072499988</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1669" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1669" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1669" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1669" t="n" s="0">
+        <v>1.752574336342E9</v>
+      </c>
+      <c r="F1669" t="n" s="0">
+        <v>103.83961540883172</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1670" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1670" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1670" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1670" t="n" s="0">
+        <v>1.752574346342E9</v>
+      </c>
+      <c r="F1670" t="n" s="0">
+        <v>103.83961540883172</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1671" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1671" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1671" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1671" t="n" s="0">
+        <v>1.752574356342E9</v>
+      </c>
+      <c r="F1671" t="n" s="0">
+        <v>103.83961540883172</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1672" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1672" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1672" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1672" t="n" s="0">
+        <v>1.752574366342E9</v>
+      </c>
+      <c r="F1672" t="n" s="0">
+        <v>99.7462972359361</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1673" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1673" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1673" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1673" t="n" s="0">
+        <v>1.752574376342E9</v>
+      </c>
+      <c r="F1673" t="n" s="0">
+        <v>99.7462972359361</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1674" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1674" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1674" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1674" t="n" s="0">
+        <v>1.752574096342E9</v>
+      </c>
+      <c r="F1674" t="n" s="0">
+        <v>485.5135890000001</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1675" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1675" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1675" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1675" t="n" s="0">
+        <v>1.752574106342E9</v>
+      </c>
+      <c r="F1675" t="n" s="0">
+        <v>586.5485890000001</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1676" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1676" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1676" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1676" t="n" s="0">
+        <v>1.752574116342E9</v>
+      </c>
+      <c r="F1676" t="n" s="0">
+        <v>687.5835890000001</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1677" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1677" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1677" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1677" t="n" s="0">
+        <v>1.752574126342E9</v>
+      </c>
+      <c r="F1677" t="n" s="0">
+        <v>1091.7569088</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1678" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1678" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1678" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1678" t="n" s="0">
+        <v>1.752574136342E9</v>
+      </c>
+      <c r="F1678" t="n" s="0">
+        <v>1231.6289088</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1679" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1679" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1679" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1679" t="n" s="0">
+        <v>1.752574146342E9</v>
+      </c>
+      <c r="F1679" t="n" s="0">
+        <v>1371.5009088000002</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1680" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1680" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1680" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1680" t="n" s="0">
+        <v>1.752574156342E9</v>
+      </c>
+      <c r="F1680" t="n" s="0">
+        <v>1625.6796335999998</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1681" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1681" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1681" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1681" t="n" s="0">
+        <v>1.752574166342E9</v>
+      </c>
+      <c r="F1681" t="n" s="0">
+        <v>1776.1303002666662</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1682" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1682" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1682" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1682" t="n" s="0">
+        <v>1.752574176342E9</v>
+      </c>
+      <c r="F1682" t="n" s="0">
+        <v>1926.5809669333328</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1683" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1683" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1683" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1683" t="n" s="0">
+        <v>1.752574186342E9</v>
+      </c>
+      <c r="F1683" t="n" s="0">
+        <v>2137.035886895734</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1684" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1684" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1684" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1684" t="n" s="0">
+        <v>1.752574196342E9</v>
+      </c>
+      <c r="F1684" t="n" s="0">
+        <v>2291.8328469210674</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1685" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1685" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1685" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1685" t="n" s="0">
+        <v>1.752574206342E9</v>
+      </c>
+      <c r="F1685" t="n" s="0">
+        <v>2446.6298069464005</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1686" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1686" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1686" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1686" t="n" s="0">
+        <v>1.752574216342E9</v>
+      </c>
+      <c r="F1686" t="n" s="0">
+        <v>2590.7439915600003</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1687" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1687" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1687" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1687" t="n" s="0">
+        <v>1.752574226342E9</v>
+      </c>
+      <c r="F1687" t="n" s="0">
+        <v>2744.90539156</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1688" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1688" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1688" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1688" t="n" s="0">
+        <v>1.752574236342E9</v>
+      </c>
+      <c r="F1688" t="n" s="0">
+        <v>2899.06679156</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1689" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1689" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1689" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1689" t="n" s="0">
+        <v>1.752574246342E9</v>
+      </c>
+      <c r="F1689" t="n" s="0">
+        <v>3121.546074507919</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1690" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1690" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1690" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1690" t="n" s="0">
+        <v>1.752574256342E9</v>
+      </c>
+      <c r="F1690" t="n" s="0">
+        <v>3279.15686555908</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1691" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1691" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1691" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1691" t="n" s="0">
+        <v>1.752574266342E9</v>
+      </c>
+      <c r="F1691" t="n" s="0">
+        <v>3436.767656610241</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1692" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1692" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1692" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1692" t="n" s="0">
+        <v>1.752574276342E9</v>
+      </c>
+      <c r="F1692" t="n" s="0">
+        <v>3668.9490091101607</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1693" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1693" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1693" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1693" t="n" s="0">
+        <v>1.752574286342E9</v>
+      </c>
+      <c r="F1693" t="n" s="0">
+        <v>3829.829671583197</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1694" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1694" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1694" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1694" t="n" s="0">
+        <v>1.752574296342E9</v>
+      </c>
+      <c r="F1694" t="n" s="0">
+        <v>3990.7103340562326</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1695" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1695" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1695" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1695" t="n" s="0">
+        <v>1.752574306342E9</v>
+      </c>
+      <c r="F1695" t="n" s="0">
+        <v>4158.524081625</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1696" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1696" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1696" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1696" t="n" s="0">
+        <v>1.752574316342E9</v>
+      </c>
+      <c r="F1696" t="n" s="0">
+        <v>4319.673456625</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1697" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1697" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1697" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1697" t="n" s="0">
+        <v>1.752574326342E9</v>
+      </c>
+      <c r="F1697" t="n" s="0">
+        <v>4480.822831625</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1698" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1698" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1698" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1698" t="n" s="0">
+        <v>1.752574336342E9</v>
+      </c>
+      <c r="F1698" t="n" s="0">
+        <v>4807.1788623005095</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1699" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1699" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1699" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1699" t="n" s="0">
+        <v>1.752574346342E9</v>
+      </c>
+      <c r="F1699" t="n" s="0">
+        <v>4807.1788623005095</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1700" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1700" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1700" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1700" t="n" s="0">
+        <v>1.752574356342E9</v>
+      </c>
+      <c r="F1700" t="n" s="0">
+        <v>4807.1788623005095</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1701" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1701" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1701" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1701" t="n" s="0">
+        <v>1.752574366342E9</v>
+      </c>
+      <c r="F1701" t="n" s="0">
+        <v>4973.061581253402</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B1702" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1702" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="D1702" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1702" t="n" s="0">
+        <v>1.752574376342E9</v>
+      </c>
+      <c r="F1702" t="n" s="0">
+        <v>4973.061581253402</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1703" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1703" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1703" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1703" t="n" s="0">
+        <v>1.752576244631E9</v>
+      </c>
+      <c r="F1703" t="n" s="0">
+        <v>577.5512270036477</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1704" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1704" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1704" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1704" t="n" s="0">
+        <v>1.752576254631E9</v>
+      </c>
+      <c r="F1704" t="n" s="0">
+        <v>594.1222990205113</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1705" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1705" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1705" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1705" t="n" s="0">
+        <v>1.752576264631E9</v>
+      </c>
+      <c r="F1705" t="n" s="0">
+        <v>605.2486529303197</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1706" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1706" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1706" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1706" t="n" s="0">
+        <v>1.752576274631E9</v>
+      </c>
+      <c r="F1706" t="n" s="0">
+        <v>622.31437124915</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1707" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1707" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1707" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1707" t="n" s="0">
+        <v>1.752576284631E9</v>
+      </c>
+      <c r="F1707" t="n" s="0">
+        <v>639.3800895679802</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1708" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1708" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1708" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1708" t="n" s="0">
+        <v>1.752576294631E9</v>
+      </c>
+      <c r="F1708" t="n" s="0">
+        <v>669.8761456744286</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1709" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1709" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1709" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1709" t="n" s="0">
+        <v>1.752576304631E9</v>
+      </c>
+      <c r="F1709" t="n" s="0">
+        <v>687.892893882473</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1710" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1710" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1710" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1710" t="n" s="0">
+        <v>1.752576314631E9</v>
+      </c>
+      <c r="F1710" t="n" s="0">
+        <v>705.9096420905175</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1711" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1711" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1711" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1711" t="n" s="0">
+        <v>1.752576324631E9</v>
+      </c>
+      <c r="F1711" t="n" s="0">
+        <v>731.5747469133964</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1712" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1712" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1712" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1712" t="n" s="0">
+        <v>1.752576334631E9</v>
+      </c>
+      <c r="F1712" t="n" s="0">
+        <v>749.6701902253752</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1713" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1713" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1713" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1713" t="n" s="0">
+        <v>1.752576344631E9</v>
+      </c>
+      <c r="F1713" t="n" s="0">
+        <v>767.7656335373539</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1714" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1714" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1714" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1714" t="n" s="0">
+        <v>1.752576354631E9</v>
+      </c>
+      <c r="F1714" t="n" s="0">
+        <v>806.6929358747158</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1715" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1715" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1715" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1715" t="n" s="0">
+        <v>1.752576364631E9</v>
+      </c>
+      <c r="F1715" t="n" s="0">
+        <v>807.5544188848983</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1716" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1716" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1716" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1716" t="n" s="0">
+        <v>1.752576374631E9</v>
+      </c>
+      <c r="F1716" t="n" s="0">
+        <v>808.4159018950808</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1717" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1717" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1717" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1717" t="n" s="0">
+        <v>1.752576384631E9</v>
+      </c>
+      <c r="F1717" t="n" s="0">
+        <v>784.9168133333334</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1718" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1718" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1718" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1718" t="n" s="0">
+        <v>1.752576394631E9</v>
+      </c>
+      <c r="F1718" t="n" s="0">
+        <v>788.3501466666668</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1719" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1719" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1719" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1719" t="n" s="0">
+        <v>1.752576404631E9</v>
+      </c>
+      <c r="F1719" t="n" s="0">
+        <v>788.7866666666667</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1720" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1720" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1720" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1720" t="n" s="0">
+        <v>1.752576414631E9</v>
+      </c>
+      <c r="F1720" t="n" s="0">
+        <v>791.6766666666667</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1721" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1721" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1721" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1721" t="n" s="0">
+        <v>1.752576424631E9</v>
+      </c>
+      <c r="F1721" t="n" s="0">
+        <v>791.6766666666667</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1722" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1722" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1722" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1722" t="n" s="0">
+        <v>1.752576434631E9</v>
+      </c>
+      <c r="F1722" t="n" s="0">
+        <v>791.6766666666667</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1723" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1723" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1723" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1723" t="n" s="0">
+        <v>1.752576444631E9</v>
+      </c>
+      <c r="F1723" t="n" s="0">
+        <v>807.99</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1724" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1724" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1724" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1724" t="n" s="0">
+        <v>1.752576454631E9</v>
+      </c>
+      <c r="F1724" t="n" s="0">
+        <v>807.99</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1725" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1725" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1725" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1725" t="n" s="0">
+        <v>1.752576464631E9</v>
+      </c>
+      <c r="F1725" t="n" s="0">
+        <v>807.99</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1726" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1726" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1726" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1726" t="n" s="0">
+        <v>1.752576474631E9</v>
+      </c>
+      <c r="F1726" t="n" s="0">
+        <v>836.4366666666667</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1727" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1727" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1727" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1727" t="n" s="0">
+        <v>1.752576484631E9</v>
+      </c>
+      <c r="F1727" t="n" s="0">
+        <v>836.4366666666667</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1728" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1728" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1728" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1728" t="n" s="0">
+        <v>1.752576494631E9</v>
+      </c>
+      <c r="F1728" t="n" s="0">
+        <v>836.4366666666667</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1729" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1729" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1729" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1729" t="n" s="0">
+        <v>1.752576504631E9</v>
+      </c>
+      <c r="F1729" t="n" s="0">
+        <v>852.3566666666667</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1730" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1730" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1730" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1730" t="n" s="0">
+        <v>1.752576514631E9</v>
+      </c>
+      <c r="F1730" t="n" s="0">
+        <v>852.3566666666667</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1731" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1731" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1731" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1731" t="n" s="0">
+        <v>1.752576524631E9</v>
+      </c>
+      <c r="F1731" t="n" s="0">
+        <v>852.3566666666667</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1732" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1732" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1732" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1732" t="n" s="0">
+        <v>1.752576534631E9</v>
+      </c>
+      <c r="F1732" t="n" s="0">
+        <v>859.6533333333334</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1733" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1733" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1733" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1733" t="n" s="0">
+        <v>1.752576544631E9</v>
+      </c>
+      <c r="F1733" t="n" s="0">
+        <v>859.6533333333334</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1734" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1734" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1734" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1734" t="n" s="0">
+        <v>1.752576244631E9</v>
+      </c>
+      <c r="F1734" t="n" s="0">
+        <v>236.8047566807827</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1735" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1735" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1735" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1735" t="n" s="0">
+        <v>1.752576254631E9</v>
+      </c>
+      <c r="F1735" t="n" s="0">
+        <v>227.49275668078266</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1736" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1736" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1736" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1736" t="n" s="0">
+        <v>1.752576264631E9</v>
+      </c>
+      <c r="F1736" t="n" s="0">
+        <v>301.6777226491187</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1737" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1737" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1737" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1737" t="n" s="0">
+        <v>1.752576274631E9</v>
+      </c>
+      <c r="F1737" t="n" s="0">
+        <v>294.03522264911874</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1738" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1738" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1738" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1738" t="n" s="0">
+        <v>1.752576284631E9</v>
+      </c>
+      <c r="F1738" t="n" s="0">
+        <v>286.39272264911875</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1739" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1739" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1739" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1739" t="n" s="0">
+        <v>1.752576294631E9</v>
+      </c>
+      <c r="F1739" t="n" s="0">
+        <v>344.3401907473666</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1740" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1740" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1740" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1740" t="n" s="0">
+        <v>1.752576304631E9</v>
+      </c>
+      <c r="F1740" t="n" s="0">
+        <v>338.4491907473666</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1741" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1741" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1741" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1741" t="n" s="0">
+        <v>1.752576314631E9</v>
+      </c>
+      <c r="F1741" t="n" s="0">
+        <v>332.5581907473666</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1742" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1742" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1742" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1742" t="n" s="0">
+        <v>1.752576324631E9</v>
+      </c>
+      <c r="F1742" t="n" s="0">
+        <v>379.7259363226714</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1743" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1743" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1743" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1743" t="n" s="0">
+        <v>1.752576334631E9</v>
+      </c>
+      <c r="F1743" t="n" s="0">
+        <v>379.7259363226714</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1744" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1744" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1744" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1744" t="n" s="0">
+        <v>1.752576344631E9</v>
+      </c>
+      <c r="F1744" t="n" s="0">
+        <v>379.7259363226714</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1745" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1745" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1745" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1745" t="n" s="0">
+        <v>1.752576354631E9</v>
+      </c>
+      <c r="F1745" t="n" s="0">
+        <v>437.57234827638433</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1746" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1746" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1746" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1746" t="n" s="0">
+        <v>1.752576364631E9</v>
+      </c>
+      <c r="F1746" t="n" s="0">
+        <v>437.57234827638433</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1747" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1747" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1747" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1747" t="n" s="0">
+        <v>1.752576374631E9</v>
+      </c>
+      <c r="F1747" t="n" s="0">
+        <v>437.57234827638433</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1748" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1748" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1748" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1748" t="n" s="0">
+        <v>1.752576384631E9</v>
+      </c>
+      <c r="F1748" t="n" s="0">
+        <v>488.89666666666665</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1749" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1749" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1749" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1749" t="n" s="0">
+        <v>1.752576394631E9</v>
+      </c>
+      <c r="F1749" t="n" s="0">
+        <v>488.89666666666665</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1750" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1750" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1750" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1750" t="n" s="0">
+        <v>1.752576404631E9</v>
+      </c>
+      <c r="F1750" t="n" s="0">
+        <v>488.89666666666665</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1751" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1751" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1751" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1751" t="n" s="0">
+        <v>1.752576414631E9</v>
+      </c>
+      <c r="F1751" t="n" s="0">
+        <v>536.11</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1752" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1752" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1752" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1752" t="n" s="0">
+        <v>1.752576424631E9</v>
+      </c>
+      <c r="F1752" t="n" s="0">
+        <v>536.11</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1753" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1753" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1753" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1753" t="n" s="0">
+        <v>1.752576434631E9</v>
+      </c>
+      <c r="F1753" t="n" s="0">
+        <v>536.11</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1754" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1754" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1754" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1754" t="n" s="0">
+        <v>1.752576444631E9</v>
+      </c>
+      <c r="F1754" t="n" s="0">
+        <v>593.0600000000001</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1755" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1755" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1755" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1755" t="n" s="0">
+        <v>1.752576454631E9</v>
+      </c>
+      <c r="F1755" t="n" s="0">
+        <v>593.0600000000001</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1756" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1756" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1756" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1756" t="n" s="0">
+        <v>1.752576464631E9</v>
+      </c>
+      <c r="F1756" t="n" s="0">
+        <v>593.0600000000001</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1757" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1757" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1757" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1757" t="n" s="0">
+        <v>1.752576474631E9</v>
+      </c>
+      <c r="F1757" t="n" s="0">
+        <v>651.6866666666665</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1758" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1758" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1758" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1758" t="n" s="0">
+        <v>1.752576484631E9</v>
+      </c>
+      <c r="F1758" t="n" s="0">
+        <v>651.6866666666665</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1759" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1759" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1759" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1759" t="n" s="0">
+        <v>1.752576494631E9</v>
+      </c>
+      <c r="F1759" t="n" s="0">
+        <v>651.6866666666665</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1760" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1760" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1760" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1760" t="n" s="0">
+        <v>1.752576504631E9</v>
+      </c>
+      <c r="F1760" t="n" s="0">
+        <v>708.3199999999999</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1761" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1761" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1761" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1761" t="n" s="0">
+        <v>1.752576514631E9</v>
+      </c>
+      <c r="F1761" t="n" s="0">
+        <v>708.3199999999999</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1762" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1762" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1762" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1762" t="n" s="0">
+        <v>1.752576524631E9</v>
+      </c>
+      <c r="F1762" t="n" s="0">
+        <v>708.3199999999999</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1763" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1763" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1763" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1763" t="n" s="0">
+        <v>1.752576534631E9</v>
+      </c>
+      <c r="F1763" t="n" s="0">
+        <v>650.9066666666668</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1764" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1764" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="D1764" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1764" t="n" s="0">
+        <v>1.752576544631E9</v>
+      </c>
+      <c r="F1764" t="n" s="0">
+        <v>650.9066666666668</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1765" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1765" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1765" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1765" t="n" s="0">
+        <v>1.752577128666E9</v>
+      </c>
+      <c r="F1765" t="n" s="0">
+        <v>597.1264621750001</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1766" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1766" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1766" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1766" t="n" s="0">
+        <v>1.752577138666E9</v>
+      </c>
+      <c r="F1766" t="n" s="0">
+        <v>592.7270872833336</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1767" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1767" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1767" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1767" t="n" s="0">
+        <v>1.752577148666E9</v>
+      </c>
+      <c r="F1767" t="n" s="0">
+        <v>582.9002539500002</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1768" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1768" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1768" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1768" t="n" s="0">
+        <v>1.752577158666E9</v>
+      </c>
+      <c r="F1768" t="n" s="0">
+        <v>573.073420616667</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1769" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1769" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1769" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1769" t="n" s="0">
+        <v>1.752577168666E9</v>
+      </c>
+      <c r="F1769" t="n" s="0">
+        <v>569.9426103000001</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1770" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1770" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1770" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1770" t="n" s="0">
+        <v>1.752577178666E9</v>
+      </c>
+      <c r="F1770" t="n" s="0">
+        <v>559.8836103000001</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1771" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1771" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1771" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1771" t="n" s="0">
+        <v>1.752577188666E9</v>
+      </c>
+      <c r="F1771" t="n" s="0">
+        <v>549.8246103000001</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1772" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1772" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1772" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1772" t="n" s="0">
+        <v>1.752577198666E9</v>
+      </c>
+      <c r="F1772" t="n" s="0">
+        <v>540.7537730650306</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1773" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1773" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1773" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1773" t="n" s="0">
+        <v>1.752577208666E9</v>
+      </c>
+      <c r="F1773" t="n" s="0">
+        <v>529.8865881999044</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1774" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1774" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1774" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1774" t="n" s="0">
+        <v>1.752577218666E9</v>
+      </c>
+      <c r="F1774" t="n" s="0">
+        <v>519.0194033347782</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1775" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1775" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1775" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1775" t="n" s="0">
+        <v>1.752577228666E9</v>
+      </c>
+      <c r="F1775" t="n" s="0">
+        <v>371.45883126</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1776" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1776" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1776" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1776" t="n" s="0">
+        <v>1.752577238666E9</v>
+      </c>
+      <c r="F1776" t="n" s="0">
+        <v>393.17103126</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1777" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1777" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1777" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1777" t="n" s="0">
+        <v>1.752577248666E9</v>
+      </c>
+      <c r="F1777" t="n" s="0">
+        <v>414.88323126</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1778" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1778" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1778" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1778" t="n" s="0">
+        <v>1.752577258666E9</v>
+      </c>
+      <c r="F1778" t="n" s="0">
+        <v>432.8110492</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1779" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1779" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1779" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1779" t="n" s="0">
+        <v>1.752577268666E9</v>
+      </c>
+      <c r="F1779" t="n" s="0">
+        <v>454.3350492</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1780" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1780" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1780" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1780" t="n" s="0">
+        <v>1.752577278666E9</v>
+      </c>
+      <c r="F1780" t="n" s="0">
+        <v>475.8590492</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1781" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1781" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1781" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1781" t="n" s="0">
+        <v>1.752577288666E9</v>
+      </c>
+      <c r="F1781" t="n" s="0">
+        <v>504.3364017909438</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1782" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1782" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1782" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1782" t="n" s="0">
+        <v>1.752577298666E9</v>
+      </c>
+      <c r="F1782" t="n" s="0">
+        <v>526.1612978628673</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1783" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1783" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1783" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1783" t="n" s="0">
+        <v>1.752577308666E9</v>
+      </c>
+      <c r="F1783" t="n" s="0">
+        <v>547.9861939347907</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1784" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1784" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1784" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1784" t="n" s="0">
+        <v>1.752577318666E9</v>
+      </c>
+      <c r="F1784" t="n" s="0">
+        <v>577.2969389875001</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1785" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1785" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1785" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1785" t="n" s="0">
+        <v>1.752577328666E9</v>
+      </c>
+      <c r="F1785" t="n" s="0">
+        <v>599.4085639875</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1786" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1786" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1786" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1786" t="n" s="0">
+        <v>1.752577338666E9</v>
+      </c>
+      <c r="F1786" t="n" s="0">
+        <v>621.5201889874999</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1787" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1787" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1787" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1787" t="n" s="0">
+        <v>1.752577348666E9</v>
+      </c>
+      <c r="F1787" t="n" s="0">
+        <v>669.2900000000002</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1788" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1788" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1788" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1788" t="n" s="0">
+        <v>1.752577358666E9</v>
+      </c>
+      <c r="F1788" t="n" s="0">
+        <v>669.2900000000001</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1789" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1789" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1789" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1789" t="n" s="0">
+        <v>1.752577368666E9</v>
+      </c>
+      <c r="F1789" t="n" s="0">
+        <v>669.2900000000001</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1790" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1790" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1790" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1790" t="n" s="0">
+        <v>1.752577378666E9</v>
+      </c>
+      <c r="F1790" t="n" s="0">
+        <v>668.7266666666668</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1791" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1791" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1791" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1791" t="n" s="0">
+        <v>1.752577388666E9</v>
+      </c>
+      <c r="F1791" t="n" s="0">
+        <v>668.7266666666667</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1792" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1792" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1792" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1792" t="n" s="0">
+        <v>1.752577398666E9</v>
+      </c>
+      <c r="F1792" t="n" s="0">
+        <v>668.7266666666667</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1793" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1793" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1793" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1793" t="n" s="0">
+        <v>1.752577408666E9</v>
+      </c>
+      <c r="F1793" t="n" s="0">
+        <v>675.0066666666669</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1794" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1794" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1794" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1794" t="n" s="0">
+        <v>1.752577418666E9</v>
+      </c>
+      <c r="F1794" t="n" s="0">
+        <v>675.0066666666667</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1795" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1795" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1795" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1795" t="n" s="0">
+        <v>1.752577428666E9</v>
+      </c>
+      <c r="F1795" t="n" s="0">
+        <v>675.0066666666667</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1796" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1796" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1796" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1796" t="n" s="0">
+        <v>1.752577128666E9</v>
+      </c>
+      <c r="F1796" t="n" s="0">
+        <v>148.6899999999999</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1797" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1797" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1797" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1797" t="n" s="0">
+        <v>1.752577138666E9</v>
+      </c>
+      <c r="F1797" t="n" s="0">
+        <v>150.42999999999992</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1798" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1798" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1798" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1798" t="n" s="0">
+        <v>1.752577148666E9</v>
+      </c>
+      <c r="F1798" t="n" s="0">
+        <v>150.4299999999999</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1799" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1799" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1799" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1799" t="n" s="0">
+        <v>1.752577158666E9</v>
+      </c>
+      <c r="F1799" t="n" s="0">
+        <v>150.4299999999999</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1800" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1800" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1800" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1800" t="n" s="0">
+        <v>1.752577168666E9</v>
+      </c>
+      <c r="F1800" t="n" s="0">
+        <v>198.8900000000002</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1801" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1801" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1801" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1801" t="n" s="0">
+        <v>1.752577178666E9</v>
+      </c>
+      <c r="F1801" t="n" s="0">
+        <v>198.89000000000016</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1802" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1802" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1802" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1802" t="n" s="0">
+        <v>1.752577188666E9</v>
+      </c>
+      <c r="F1802" t="n" s="0">
+        <v>198.89000000000016</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1803" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1803" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1803" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1803" t="n" s="0">
+        <v>1.752577198666E9</v>
+      </c>
+      <c r="F1803" t="n" s="0">
+        <v>225.8324969166781</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1804" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1804" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1804" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1804" t="n" s="0">
+        <v>1.752577208666E9</v>
+      </c>
+      <c r="F1804" t="n" s="0">
+        <v>225.83249691667805</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1805" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1805" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1805" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1805" t="n" s="0">
+        <v>1.752577218666E9</v>
+      </c>
+      <c r="F1805" t="n" s="0">
+        <v>225.83249691667805</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1806" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1806" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1806" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1806" t="n" s="0">
+        <v>1.752577228666E9</v>
+      </c>
+      <c r="F1806" t="n" s="0">
+        <v>266.99666666666667</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1807" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1807" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1807" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1807" t="n" s="0">
+        <v>1.752577238666E9</v>
+      </c>
+      <c r="F1807" t="n" s="0">
+        <v>266.99666666666667</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1808" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1808" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1808" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1808" t="n" s="0">
+        <v>1.752577248666E9</v>
+      </c>
+      <c r="F1808" t="n" s="0">
+        <v>266.99666666666667</v>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1809" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1809" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1809" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1809" t="n" s="0">
+        <v>1.752577258666E9</v>
+      </c>
+      <c r="F1809" t="n" s="0">
+        <v>295.93666666666667</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1810" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1810" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1810" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1810" t="n" s="0">
+        <v>1.752577268666E9</v>
+      </c>
+      <c r="F1810" t="n" s="0">
+        <v>295.93666666666667</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1811" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1811" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1811" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1811" t="n" s="0">
+        <v>1.752577278666E9</v>
+      </c>
+      <c r="F1811" t="n" s="0">
+        <v>295.93666666666667</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1812" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1812" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1812" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1812" t="n" s="0">
+        <v>1.752577288666E9</v>
+      </c>
+      <c r="F1812" t="n" s="0">
+        <v>332.9454335354313</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1813" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1813" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1813" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1813" t="n" s="0">
+        <v>1.752577298666E9</v>
+      </c>
+      <c r="F1813" t="n" s="0">
+        <v>332.9454335354312</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1814" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1814" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1814" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1814" t="n" s="0">
+        <v>1.752577308666E9</v>
+      </c>
+      <c r="F1814" t="n" s="0">
+        <v>332.9454335354312</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1815" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1815" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1815" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1815" t="n" s="0">
+        <v>1.752577318666E9</v>
+      </c>
+      <c r="F1815" t="n" s="0">
+        <v>372.90999999999997</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1816" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1816" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1816" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1816" t="n" s="0">
+        <v>1.752577328666E9</v>
+      </c>
+      <c r="F1816" t="n" s="0">
+        <v>372.9099999999999</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1817" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1817" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1817" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1817" t="n" s="0">
+        <v>1.752577338666E9</v>
+      </c>
+      <c r="F1817" t="n" s="0">
+        <v>372.9099999999999</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1818" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1818" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1818" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1818" t="n" s="0">
+        <v>1.752577348666E9</v>
+      </c>
+      <c r="F1818" t="n" s="0">
+        <v>414.2866666666668</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1819" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1819" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1819" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1819" t="n" s="0">
+        <v>1.752577358666E9</v>
+      </c>
+      <c r="F1819" t="n" s="0">
+        <v>414.2866666666667</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1820" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1820" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1820" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1820" t="n" s="0">
+        <v>1.752577368666E9</v>
+      </c>
+      <c r="F1820" t="n" s="0">
+        <v>414.2866666666667</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1821" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1821" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1821" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1821" t="n" s="0">
+        <v>1.752577378666E9</v>
+      </c>
+      <c r="F1821" t="n" s="0">
+        <v>446.686666666667</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1822" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1822" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1822" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1822" t="n" s="0">
+        <v>1.752577388666E9</v>
+      </c>
+      <c r="F1822" t="n" s="0">
+        <v>446.68666666666695</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1823" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1823" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1823" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1823" t="n" s="0">
+        <v>1.752577398666E9</v>
+      </c>
+      <c r="F1823" t="n" s="0">
+        <v>446.68666666666695</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1824" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1824" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1824" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1824" t="n" s="0">
+        <v>1.752577408666E9</v>
+      </c>
+      <c r="F1824" t="n" s="0">
+        <v>474.76333333333355</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1825" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1825" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1825" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1825" t="n" s="0">
+        <v>1.752577418666E9</v>
+      </c>
+      <c r="F1825" t="n" s="0">
+        <v>474.7633333333335</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1826" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1826" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="D1826" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1826" t="n" s="0">
+        <v>1.752577428666E9</v>
+      </c>
+      <c r="F1826" t="n" s="0">
+        <v>474.7633333333335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Python/results/metrics_data.xlsx
+++ b/Python/results/metrics_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6127" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6939" uniqueCount="570">
   <si>
     <t>Pattern</t>
   </si>
@@ -1555,6 +1555,174 @@
   </si>
   <si>
     <t>20250715_130348</t>
+  </si>
+  <si>
+    <t>2025-07-17 14:46:12</t>
+  </si>
+  <si>
+    <t>5959.583333333334</t>
+  </si>
+  <si>
+    <t>19.865277777777777</t>
+  </si>
+  <si>
+    <t>690415024.4740741</t>
+  </si>
+  <si>
+    <t>1274899450.7925925</t>
+  </si>
+  <si>
+    <t>2622806058.5703707</t>
+  </si>
+  <si>
+    <t>1.3202966945190987E8</t>
+  </si>
+  <si>
+    <t>16.58357230417861</t>
+  </si>
+  <si>
+    <t>2.0572650313244685</t>
+  </si>
+  <si>
+    <t>1.0981082839506173</t>
+  </si>
+  <si>
+    <t>329.43727037037036</t>
+  </si>
+  <si>
+    <t>5298.6113888888885</t>
+  </si>
+  <si>
+    <t>16.08382495074682</t>
+  </si>
+  <si>
+    <t>20250717_144612</t>
+  </si>
+  <si>
+    <t>2025-07-17 14:55:03</t>
+  </si>
+  <si>
+    <t>5033.69</t>
+  </si>
+  <si>
+    <t>16.778966666666665</t>
+  </si>
+  <si>
+    <t>619206393.7555556</t>
+  </si>
+  <si>
+    <t>1035755574.4740741</t>
+  </si>
+  <si>
+    <t>2413997879.9555554</t>
+  </si>
+  <si>
+    <t>1.438704735465765E8</t>
+  </si>
+  <si>
+    <t>21.45543329048869</t>
+  </si>
+  <si>
+    <t>2.330663661821286</t>
+  </si>
+  <si>
+    <t>1.2000000000000002</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>6080.689655172414</t>
+  </si>
+  <si>
+    <t>16.89080459770115</t>
+  </si>
+  <si>
+    <t>20250717_145503</t>
+  </si>
+  <si>
+    <t>2025-07-17 14:57:00</t>
+  </si>
+  <si>
+    <t>4132.75</t>
+  </si>
+  <si>
+    <t>13.775833333333335</t>
+  </si>
+  <si>
+    <t>531570195.67777777</t>
+  </si>
+  <si>
+    <t>897215317.6185186</t>
+  </si>
+  <si>
+    <t>2090992645.7222223</t>
+  </si>
+  <si>
+    <t>1.5178701680882382E8</t>
+  </si>
+  <si>
+    <t>26.65837851142785</t>
+  </si>
+  <si>
+    <t>2.330536053789575</t>
+  </si>
+  <si>
+    <t>1.2241379310344829</t>
+  </si>
+  <si>
+    <t>367.2413793103448</t>
+  </si>
+  <si>
+    <t>6131.379310344828</t>
+  </si>
+  <si>
+    <t>16.695774647887326</t>
+  </si>
+  <si>
+    <t>20250717_145700</t>
+  </si>
+  <si>
+    <t>2025-07-17 15:03:08</t>
+  </si>
+  <si>
+    <t>4363.466666666666</t>
+  </si>
+  <si>
+    <t>14.544888888888888</t>
+  </si>
+  <si>
+    <t>574836256.4962963</t>
+  </si>
+  <si>
+    <t>968121957.0444444</t>
+  </si>
+  <si>
+    <t>2266575645.5444446</t>
+  </si>
+  <si>
+    <t>1.5583313580868423E8</t>
+  </si>
+  <si>
+    <t>25.177703270836016</t>
+  </si>
+  <si>
+    <t>2.3412088002466316</t>
+  </si>
+  <si>
+    <t>1.220689655172414</t>
+  </si>
+  <si>
+    <t>366.2068965517242</t>
+  </si>
+  <si>
+    <t>5972.068965517242</t>
+  </si>
+  <si>
+    <t>16.30790960451977</t>
+  </si>
+  <si>
+    <t>20250717_150309</t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="17.45703125"/>
@@ -3634,6 +3802,218 @@
         <v>281</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>514</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>515</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>516</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>517</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>518</v>
+      </c>
+      <c r="H39" t="s" s="0">
+        <v>519</v>
+      </c>
+      <c r="I39" t="s" s="0">
+        <v>520</v>
+      </c>
+      <c r="J39" t="s" s="0">
+        <v>521</v>
+      </c>
+      <c r="K39" t="s" s="0">
+        <v>522</v>
+      </c>
+      <c r="L39" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M39" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N39" t="s" s="0">
+        <v>523</v>
+      </c>
+      <c r="O39" t="s" s="0">
+        <v>524</v>
+      </c>
+      <c r="P39" t="s" s="0">
+        <v>525</v>
+      </c>
+      <c r="Q39" t="s" s="0">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>528</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>529</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>530</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>531</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>532</v>
+      </c>
+      <c r="H40" t="s" s="0">
+        <v>533</v>
+      </c>
+      <c r="I40" t="s" s="0">
+        <v>534</v>
+      </c>
+      <c r="J40" t="s" s="0">
+        <v>535</v>
+      </c>
+      <c r="K40" t="s" s="0">
+        <v>536</v>
+      </c>
+      <c r="L40" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M40" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N40" t="s" s="0">
+        <v>537</v>
+      </c>
+      <c r="O40" t="s" s="0">
+        <v>538</v>
+      </c>
+      <c r="P40" t="s" s="0">
+        <v>539</v>
+      </c>
+      <c r="Q40" t="s" s="0">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>543</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>544</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="H41" t="s" s="0">
+        <v>547</v>
+      </c>
+      <c r="I41" t="s" s="0">
+        <v>548</v>
+      </c>
+      <c r="J41" t="s" s="0">
+        <v>549</v>
+      </c>
+      <c r="K41" t="s" s="0">
+        <v>550</v>
+      </c>
+      <c r="L41" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M41" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N41" t="s" s="0">
+        <v>551</v>
+      </c>
+      <c r="O41" t="s" s="0">
+        <v>552</v>
+      </c>
+      <c r="P41" t="s" s="0">
+        <v>553</v>
+      </c>
+      <c r="Q41" t="s" s="0">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>556</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>557</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>558</v>
+      </c>
+      <c r="F42" t="s" s="0">
+        <v>559</v>
+      </c>
+      <c r="G42" t="s" s="0">
+        <v>560</v>
+      </c>
+      <c r="H42" t="s" s="0">
+        <v>561</v>
+      </c>
+      <c r="I42" t="s" s="0">
+        <v>562</v>
+      </c>
+      <c r="J42" t="s" s="0">
+        <v>563</v>
+      </c>
+      <c r="K42" t="s" s="0">
+        <v>564</v>
+      </c>
+      <c r="L42" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="M42" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="N42" t="s" s="0">
+        <v>565</v>
+      </c>
+      <c r="O42" t="s" s="0">
+        <v>566</v>
+      </c>
+      <c r="P42" t="s" s="0">
+        <v>567</v>
+      </c>
+      <c r="Q42" t="s" s="0">
+        <v>568</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -3641,7 +4021,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F1826"/>
+  <dimension ref="A1:F2074"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="17.45703125"/>
@@ -40172,6 +40552,4966 @@
         <v>474.7633333333335</v>
       </c>
     </row>
+    <row r="1827">
+      <c r="A1827" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1827" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1827" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1827" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1827" t="n" s="0">
+        <v>1.752756071459E9</v>
+      </c>
+      <c r="F1827" t="n" s="0">
+        <v>535.3618669500001</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1828" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1828" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1828" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1828" t="n" s="0">
+        <v>1.752756081459E9</v>
+      </c>
+      <c r="F1828" t="n" s="0">
+        <v>545.1133669500001</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1829" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1829" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1829" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1829" t="n" s="0">
+        <v>1.752756091459E9</v>
+      </c>
+      <c r="F1829" t="n" s="0">
+        <v>422.13325303333335</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1830" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1830" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1830" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1830" t="n" s="0">
+        <v>1.752756101459E9</v>
+      </c>
+      <c r="F1830" t="n" s="0">
+        <v>454.8355863666667</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1831" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1831" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1831" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1831" t="n" s="0">
+        <v>1.752756111459E9</v>
+      </c>
+      <c r="F1831" t="n" s="0">
+        <v>487.53791970000003</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1832" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1832" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1832" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1832" t="n" s="0">
+        <v>1.752756121459E9</v>
+      </c>
+      <c r="F1832" t="n" s="0">
+        <v>475.51285127499995</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1833" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1833" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1833" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1833" t="n" s="0">
+        <v>1.752756131459E9</v>
+      </c>
+      <c r="F1833" t="n" s="0">
+        <v>508.394601275</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1834" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1834" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1834" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1834" t="n" s="0">
+        <v>1.752756141459E9</v>
+      </c>
+      <c r="F1834" t="n" s="0">
+        <v>541.276351275</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1835" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1835" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1835" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1835" t="n" s="0">
+        <v>1.752756151459E9</v>
+      </c>
+      <c r="F1835" t="n" s="0">
+        <v>548.88199646</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1836" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1836" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1836" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1836" t="n" s="0">
+        <v>1.752756161459E9</v>
+      </c>
+      <c r="F1836" t="n" s="0">
+        <v>580.31619646</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1837" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1837" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1837" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1837" t="n" s="0">
+        <v>1.752756171459E9</v>
+      </c>
+      <c r="F1837" t="n" s="0">
+        <v>611.75039646</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1838" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1838" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1838" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1838" t="n" s="0">
+        <v>1.752756181459E9</v>
+      </c>
+      <c r="F1838" t="n" s="0">
+        <v>631.4084362666667</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1839" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1839" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1839" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1839" t="n" s="0">
+        <v>1.752756191459E9</v>
+      </c>
+      <c r="F1839" t="n" s="0">
+        <v>662.2671029333334</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1840" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1840" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1840" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1840" t="n" s="0">
+        <v>1.752756201459E9</v>
+      </c>
+      <c r="F1840" t="n" s="0">
+        <v>693.1257695999999</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1841" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1841" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1841" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1841" t="n" s="0">
+        <v>1.752756211459E9</v>
+      </c>
+      <c r="F1841" t="n" s="0">
+        <v>712.0873227571428</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1842" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1842" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1842" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1842" t="n" s="0">
+        <v>1.752756221459E9</v>
+      </c>
+      <c r="F1842" t="n" s="0">
+        <v>742.4388941857143</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1843" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1843" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1843" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1843" t="n" s="0">
+        <v>1.752756231459E9</v>
+      </c>
+      <c r="F1843" t="n" s="0">
+        <v>772.7904656142857</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1844" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1844" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1844" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1844" t="n" s="0">
+        <v>1.752756241459E9</v>
+      </c>
+      <c r="F1844" t="n" s="0">
+        <v>793.1080065875001</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1845" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1845" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1845" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1845" t="n" s="0">
+        <v>1.752756251459E9</v>
+      </c>
+      <c r="F1845" t="n" s="0">
+        <v>823.0803815874999</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1846" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1846" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1846" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1846" t="n" s="0">
+        <v>1.752756261459E9</v>
+      </c>
+      <c r="F1846" t="n" s="0">
+        <v>899.1712500000001</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1847" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1847" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1847" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1847" t="n" s="0">
+        <v>1.752756271459E9</v>
+      </c>
+      <c r="F1847" t="n" s="0">
+        <v>889.1566666666668</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1848" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1848" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1848" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1848" t="n" s="0">
+        <v>1.752756281459E9</v>
+      </c>
+      <c r="F1848" t="n" s="0">
+        <v>889.1566666666668</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1849" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1849" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1849" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1849" t="n" s="0">
+        <v>1.752756291459E9</v>
+      </c>
+      <c r="F1849" t="n" s="0">
+        <v>889.1566666666668</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1850" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1850" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1850" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1850" t="n" s="0">
+        <v>1.752756301459E9</v>
+      </c>
+      <c r="F1850" t="n" s="0">
+        <v>845.7066666666667</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1851" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1851" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1851" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1851" t="n" s="0">
+        <v>1.752756311459E9</v>
+      </c>
+      <c r="F1851" t="n" s="0">
+        <v>845.7066666666667</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1852" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1852" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1852" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1852" t="n" s="0">
+        <v>1.752756321459E9</v>
+      </c>
+      <c r="F1852" t="n" s="0">
+        <v>845.7066666666667</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1853" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1853" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1853" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1853" t="n" s="0">
+        <v>1.752756331459E9</v>
+      </c>
+      <c r="F1853" t="n" s="0">
+        <v>815.74</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1854" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1854" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1854" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1854" t="n" s="0">
+        <v>1.752756341459E9</v>
+      </c>
+      <c r="F1854" t="n" s="0">
+        <v>815.74</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1855" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1855" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1855" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1855" t="n" s="0">
+        <v>1.752756351459E9</v>
+      </c>
+      <c r="F1855" t="n" s="0">
+        <v>815.74</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1856" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1856" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1856" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1856" t="n" s="0">
+        <v>1.752756361459E9</v>
+      </c>
+      <c r="F1856" t="n" s="0">
+        <v>818.2366666666667</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1857" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1857" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1857" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1857" t="n" s="0">
+        <v>1.752756371459E9</v>
+      </c>
+      <c r="F1857" t="n" s="0">
+        <v>818.2366666666667</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1858" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1858" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1858" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1858" t="n" s="0">
+        <v>1.752756071459E9</v>
+      </c>
+      <c r="F1858" t="n" s="0">
+        <v>274.2459316666669</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1859" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1859" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1859" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1859" t="n" s="0">
+        <v>1.752756081459E9</v>
+      </c>
+      <c r="F1859" t="n" s="0">
+        <v>271.6292650000002</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1860" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1860" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1860" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1860" t="n" s="0">
+        <v>1.752756091459E9</v>
+      </c>
+      <c r="F1860" t="n" s="0">
+        <v>870.3033669700001</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1861" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1861" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1861" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1861" t="n" s="0">
+        <v>1.752756101459E9</v>
+      </c>
+      <c r="F1861" t="n" s="0">
+        <v>899.9902669700001</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1862" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1862" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1862" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1862" t="n" s="0">
+        <v>1.752756111459E9</v>
+      </c>
+      <c r="F1862" t="n" s="0">
+        <v>929.6771669700001</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1863" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1863" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1863" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1863" t="n" s="0">
+        <v>1.752756121459E9</v>
+      </c>
+      <c r="F1863" t="n" s="0">
+        <v>1759.5451588333337</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1864" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1864" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1864" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1864" t="n" s="0">
+        <v>1.752756131459E9</v>
+      </c>
+      <c r="F1864" t="n" s="0">
+        <v>1826.513492166667</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1865" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1865" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1865" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1865" t="n" s="0">
+        <v>1.752756141459E9</v>
+      </c>
+      <c r="F1865" t="n" s="0">
+        <v>1893.4818255</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1866" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1866" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1866" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1866" t="n" s="0">
+        <v>1.752756151459E9</v>
+      </c>
+      <c r="F1866" t="n" s="0">
+        <v>2409.4319390142855</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1867" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1867" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1867" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1867" t="n" s="0">
+        <v>1.752756161459E9</v>
+      </c>
+      <c r="F1867" t="n" s="0">
+        <v>2512.1300818714285</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1868" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1868" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1868" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1868" t="n" s="0">
+        <v>1.752756171459E9</v>
+      </c>
+      <c r="F1868" t="n" s="0">
+        <v>2614.8282247285715</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1869" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1869" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1869" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1869" t="n" s="0">
+        <v>1.752756181459E9</v>
+      </c>
+      <c r="F1869" t="n" s="0">
+        <v>3049.0562151000004</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1870" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1870" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1870" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1870" t="n" s="0">
+        <v>1.752756191459E9</v>
+      </c>
+      <c r="F1870" t="n" s="0">
+        <v>3164.2832151</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1871" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1871" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1871" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1871" t="n" s="0">
+        <v>1.752756201459E9</v>
+      </c>
+      <c r="F1871" t="n" s="0">
+        <v>3456.81</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1872" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1872" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1872" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1872" t="n" s="0">
+        <v>1.752756211459E9</v>
+      </c>
+      <c r="F1872" t="n" s="0">
+        <v>3681.2033333333334</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1873" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1873" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1873" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1873" t="n" s="0">
+        <v>1.752756221459E9</v>
+      </c>
+      <c r="F1873" t="n" s="0">
+        <v>3681.2033333333334</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1874" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1874" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1874" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1874" t="n" s="0">
+        <v>1.752756231459E9</v>
+      </c>
+      <c r="F1874" t="n" s="0">
+        <v>3681.2033333333334</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1875" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1875" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1875" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1875" t="n" s="0">
+        <v>1.752756241459E9</v>
+      </c>
+      <c r="F1875" t="n" s="0">
+        <v>4285.213333333333</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1876" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1876" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1876" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1876" t="n" s="0">
+        <v>1.752756251459E9</v>
+      </c>
+      <c r="F1876" t="n" s="0">
+        <v>4285.213333333333</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1877" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1877" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1877" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1877" t="n" s="0">
+        <v>1.752756261459E9</v>
+      </c>
+      <c r="F1877" t="n" s="0">
+        <v>4285.213333333333</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1878" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1878" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1878" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1878" t="n" s="0">
+        <v>1.752756271459E9</v>
+      </c>
+      <c r="F1878" t="n" s="0">
+        <v>4853.42</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1879" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1879" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1879" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1879" t="n" s="0">
+        <v>1.752756281459E9</v>
+      </c>
+      <c r="F1879" t="n" s="0">
+        <v>4853.42</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1880" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1880" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1880" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1880" t="n" s="0">
+        <v>1.752756291459E9</v>
+      </c>
+      <c r="F1880" t="n" s="0">
+        <v>4853.42</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1881" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1881" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1881" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1881" t="n" s="0">
+        <v>1.752756301459E9</v>
+      </c>
+      <c r="F1881" t="n" s="0">
+        <v>5459.13</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1882" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1882" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1882" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1882" t="n" s="0">
+        <v>1.752756311459E9</v>
+      </c>
+      <c r="F1882" t="n" s="0">
+        <v>5459.13</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1883" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1883" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1883" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1883" t="n" s="0">
+        <v>1.752756321459E9</v>
+      </c>
+      <c r="F1883" t="n" s="0">
+        <v>5459.13</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1884" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1884" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1884" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1884" t="n" s="0">
+        <v>1.752756331459E9</v>
+      </c>
+      <c r="F1884" t="n" s="0">
+        <v>5961.876666666667</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1885" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1885" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1885" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1885" t="n" s="0">
+        <v>1.752756341459E9</v>
+      </c>
+      <c r="F1885" t="n" s="0">
+        <v>5961.876666666667</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1886" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1886" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1886" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1886" t="n" s="0">
+        <v>1.752756351459E9</v>
+      </c>
+      <c r="F1886" t="n" s="0">
+        <v>5961.876666666667</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1887" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1887" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1887" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1887" t="n" s="0">
+        <v>1.752756361459E9</v>
+      </c>
+      <c r="F1887" t="n" s="0">
+        <v>5959.583333333334</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1888" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1888" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="D1888" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1888" t="n" s="0">
+        <v>1.752756371459E9</v>
+      </c>
+      <c r="F1888" t="n" s="0">
+        <v>5959.583333333334</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1889" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1889" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1889" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1889" t="n" s="0">
+        <v>1.752756603276E9</v>
+      </c>
+      <c r="F1889" t="n" s="0">
+        <v>1063.2066666666667</v>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1890" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1890" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1890" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1890" t="n" s="0">
+        <v>1.752756613276E9</v>
+      </c>
+      <c r="F1890" t="n" s="0">
+        <v>1063.2066666666667</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1891" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1891" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1891" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1891" t="n" s="0">
+        <v>1.752756623276E9</v>
+      </c>
+      <c r="F1891" t="n" s="0">
+        <v>1080.1266666666668</v>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1892" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1892" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1892" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1892" t="n" s="0">
+        <v>1.752756633276E9</v>
+      </c>
+      <c r="F1892" t="n" s="0">
+        <v>1080.1266666666668</v>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1893" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1893" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1893" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1893" t="n" s="0">
+        <v>1.752756643276E9</v>
+      </c>
+      <c r="F1893" t="n" s="0">
+        <v>1080.1266666666668</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1894" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1894" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1894" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1894" t="n" s="0">
+        <v>1.752756653276E9</v>
+      </c>
+      <c r="F1894" t="n" s="0">
+        <v>1085.8766666666666</v>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1895" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1895" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1895" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1895" t="n" s="0">
+        <v>1.752756663276E9</v>
+      </c>
+      <c r="F1895" t="n" s="0">
+        <v>1085.8766666666666</v>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1896" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1896" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1896" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1896" t="n" s="0">
+        <v>1.752756673276E9</v>
+      </c>
+      <c r="F1896" t="n" s="0">
+        <v>1085.8766666666666</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1897" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1897" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1897" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1897" t="n" s="0">
+        <v>1.752756683276E9</v>
+      </c>
+      <c r="F1897" t="n" s="0">
+        <v>1059.8866666666668</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1898" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1898" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1898" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1898" t="n" s="0">
+        <v>1.752756693276E9</v>
+      </c>
+      <c r="F1898" t="n" s="0">
+        <v>1059.8866666666668</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1899" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1899" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1899" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1899" t="n" s="0">
+        <v>1.752756703276E9</v>
+      </c>
+      <c r="F1899" t="n" s="0">
+        <v>1059.8866666666668</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1900" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1900" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1900" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1900" t="n" s="0">
+        <v>1.752756713276E9</v>
+      </c>
+      <c r="F1900" t="n" s="0">
+        <v>1031.5666666666668</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1901" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1901" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1901" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1901" t="n" s="0">
+        <v>1.752756723276E9</v>
+      </c>
+      <c r="F1901" t="n" s="0">
+        <v>1031.5666666666668</v>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1902" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1902" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1902" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1902" t="n" s="0">
+        <v>1.752756733276E9</v>
+      </c>
+      <c r="F1902" t="n" s="0">
+        <v>1031.5666666666668</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1903" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1903" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1903" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1903" t="n" s="0">
+        <v>1.752756743276E9</v>
+      </c>
+      <c r="F1903" t="n" s="0">
+        <v>995.6166666666667</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1904" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1904" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1904" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1904" t="n" s="0">
+        <v>1.752756753276E9</v>
+      </c>
+      <c r="F1904" t="n" s="0">
+        <v>995.6166666666667</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1905" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1905" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1905" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1905" t="n" s="0">
+        <v>1.752756763276E9</v>
+      </c>
+      <c r="F1905" t="n" s="0">
+        <v>995.6166666666667</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1906" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1906" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1906" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1906" t="n" s="0">
+        <v>1.752756773276E9</v>
+      </c>
+      <c r="F1906" t="n" s="0">
+        <v>959.2833333333334</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1907" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1907" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1907" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1907" t="n" s="0">
+        <v>1.752756783276E9</v>
+      </c>
+      <c r="F1907" t="n" s="0">
+        <v>959.2833333333334</v>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1908" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1908" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1908" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1908" t="n" s="0">
+        <v>1.752756793276E9</v>
+      </c>
+      <c r="F1908" t="n" s="0">
+        <v>959.2833333333334</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1909" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1909" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1909" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1909" t="n" s="0">
+        <v>1.752756803276E9</v>
+      </c>
+      <c r="F1909" t="n" s="0">
+        <v>933.4966666666667</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1910" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1910" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1910" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1910" t="n" s="0">
+        <v>1.752756813276E9</v>
+      </c>
+      <c r="F1910" t="n" s="0">
+        <v>933.4966666666667</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1911" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1911" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1911" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1911" t="n" s="0">
+        <v>1.752756823276E9</v>
+      </c>
+      <c r="F1911" t="n" s="0">
+        <v>933.4966666666667</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1912" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1912" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1912" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1912" t="n" s="0">
+        <v>1.752756833276E9</v>
+      </c>
+      <c r="F1912" t="n" s="0">
+        <v>932.8833333333332</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1913" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1913" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1913" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1913" t="n" s="0">
+        <v>1.752756843276E9</v>
+      </c>
+      <c r="F1913" t="n" s="0">
+        <v>932.8833333333332</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1914" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1914" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1914" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1914" t="n" s="0">
+        <v>1.752756853276E9</v>
+      </c>
+      <c r="F1914" t="n" s="0">
+        <v>932.8833333333332</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1915" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1915" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1915" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1915" t="n" s="0">
+        <v>1.752756863276E9</v>
+      </c>
+      <c r="F1915" t="n" s="0">
+        <v>907.1500000000001</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1916" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1916" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1916" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1916" t="n" s="0">
+        <v>1.752756873276E9</v>
+      </c>
+      <c r="F1916" t="n" s="0">
+        <v>907.1500000000001</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1917" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1917" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1917" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1917" t="n" s="0">
+        <v>1.752756883276E9</v>
+      </c>
+      <c r="F1917" t="n" s="0">
+        <v>907.1500000000001</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1918" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1918" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1918" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1918" t="n" s="0">
+        <v>1.752756893276E9</v>
+      </c>
+      <c r="F1918" t="n" s="0">
+        <v>898.28</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1919" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1919" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1919" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1919" t="n" s="0">
+        <v>1.752756903276E9</v>
+      </c>
+      <c r="F1919" t="n" s="0">
+        <v>898.28</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1920" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1920" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1920" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1920" t="n" s="0">
+        <v>1.752756603276E9</v>
+      </c>
+      <c r="F1920" t="n" s="0">
+        <v>1017.5766666666668</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1921" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1921" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1921" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1921" t="n" s="0">
+        <v>1.752756613276E9</v>
+      </c>
+      <c r="F1921" t="n" s="0">
+        <v>1017.5766666666668</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1922" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1922" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1922" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1922" t="n" s="0">
+        <v>1.752756623276E9</v>
+      </c>
+      <c r="F1922" t="n" s="0">
+        <v>684.4399999999999</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1923" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1923" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1923" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1923" t="n" s="0">
+        <v>1.752756633276E9</v>
+      </c>
+      <c r="F1923" t="n" s="0">
+        <v>684.4399999999999</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1924" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1924" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1924" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1924" t="n" s="0">
+        <v>1.752756643276E9</v>
+      </c>
+      <c r="F1924" t="n" s="0">
+        <v>684.4399999999999</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1925" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1925" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1925" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1925" t="n" s="0">
+        <v>1.752756653276E9</v>
+      </c>
+      <c r="F1925" t="n" s="0">
+        <v>1030.263333333333</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1926" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1926" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1926" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1926" t="n" s="0">
+        <v>1.752756663276E9</v>
+      </c>
+      <c r="F1926" t="n" s="0">
+        <v>1030.263333333333</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1927" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1927" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1927" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1927" t="n" s="0">
+        <v>1.752756673276E9</v>
+      </c>
+      <c r="F1927" t="n" s="0">
+        <v>1030.263333333333</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1928" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1928" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1928" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1928" t="n" s="0">
+        <v>1.752756683276E9</v>
+      </c>
+      <c r="F1928" t="n" s="0">
+        <v>1586.2200000000005</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1929" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1929" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1929" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1929" t="n" s="0">
+        <v>1.752756693276E9</v>
+      </c>
+      <c r="F1929" t="n" s="0">
+        <v>1586.2200000000005</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1930" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1930" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1930" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1930" t="n" s="0">
+        <v>1.752756703276E9</v>
+      </c>
+      <c r="F1930" t="n" s="0">
+        <v>1586.2200000000005</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1931" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1931" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1931" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1931" t="n" s="0">
+        <v>1.752756713276E9</v>
+      </c>
+      <c r="F1931" t="n" s="0">
+        <v>2134.466666666667</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1932" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1932" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1932" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1932" t="n" s="0">
+        <v>1.752756723276E9</v>
+      </c>
+      <c r="F1932" t="n" s="0">
+        <v>2134.466666666667</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1933" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1933" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1933" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1933" t="n" s="0">
+        <v>1.752756733276E9</v>
+      </c>
+      <c r="F1933" t="n" s="0">
+        <v>2134.466666666667</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1934" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1934" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1934" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1934" t="n" s="0">
+        <v>1.752756743276E9</v>
+      </c>
+      <c r="F1934" t="n" s="0">
+        <v>2657.0066666666667</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1935" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1935" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1935" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1935" t="n" s="0">
+        <v>1.752756753276E9</v>
+      </c>
+      <c r="F1935" t="n" s="0">
+        <v>2657.0066666666667</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1936" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1936" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1936" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1936" t="n" s="0">
+        <v>1.752756763276E9</v>
+      </c>
+      <c r="F1936" t="n" s="0">
+        <v>2657.0066666666667</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1937" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1937" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1937" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1937" t="n" s="0">
+        <v>1.752756773276E9</v>
+      </c>
+      <c r="F1937" t="n" s="0">
+        <v>3190.6766666666667</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1938" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1938" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1938" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1938" t="n" s="0">
+        <v>1.752756783276E9</v>
+      </c>
+      <c r="F1938" t="n" s="0">
+        <v>3190.6766666666667</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1939" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1939" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1939" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1939" t="n" s="0">
+        <v>1.752756793276E9</v>
+      </c>
+      <c r="F1939" t="n" s="0">
+        <v>3190.6766666666667</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1940" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1940" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1940" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1940" t="n" s="0">
+        <v>1.752756803276E9</v>
+      </c>
+      <c r="F1940" t="n" s="0">
+        <v>3640.1800000000003</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1941" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1941" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1941" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1941" t="n" s="0">
+        <v>1.752756813276E9</v>
+      </c>
+      <c r="F1941" t="n" s="0">
+        <v>3640.1800000000003</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1942" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1942" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1942" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1942" t="n" s="0">
+        <v>1.752756823276E9</v>
+      </c>
+      <c r="F1942" t="n" s="0">
+        <v>3640.1800000000003</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1943" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1943" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1943" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1943" t="n" s="0">
+        <v>1.752756833276E9</v>
+      </c>
+      <c r="F1943" t="n" s="0">
+        <v>4210.066666666667</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1944" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1944" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1944" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1944" t="n" s="0">
+        <v>1.752756843276E9</v>
+      </c>
+      <c r="F1944" t="n" s="0">
+        <v>4210.066666666667</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1945" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1945" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1945" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1945" t="n" s="0">
+        <v>1.752756853276E9</v>
+      </c>
+      <c r="F1945" t="n" s="0">
+        <v>4210.066666666667</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1946" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1946" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1946" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1946" t="n" s="0">
+        <v>1.752756863276E9</v>
+      </c>
+      <c r="F1946" t="n" s="0">
+        <v>4753.796666666666</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1947" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1947" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1947" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1947" t="n" s="0">
+        <v>1.752756873276E9</v>
+      </c>
+      <c r="F1947" t="n" s="0">
+        <v>4753.796666666666</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1948" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1948" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1948" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1948" t="n" s="0">
+        <v>1.752756883276E9</v>
+      </c>
+      <c r="F1948" t="n" s="0">
+        <v>4753.796666666666</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1949" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1949" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1949" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1949" t="n" s="0">
+        <v>1.752756893276E9</v>
+      </c>
+      <c r="F1949" t="n" s="0">
+        <v>5033.69</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1950" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1950" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="D1950" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1950" t="n" s="0">
+        <v>1.752756903276E9</v>
+      </c>
+      <c r="F1950" t="n" s="0">
+        <v>5033.69</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1951" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1951" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1951" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1951" t="n" s="0">
+        <v>1.752756720006E9</v>
+      </c>
+      <c r="F1951" t="n" s="0">
+        <v>1031.5666666666668</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1952" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1952" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1952" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1952" t="n" s="0">
+        <v>1.752756730006E9</v>
+      </c>
+      <c r="F1952" t="n" s="0">
+        <v>1031.5666666666668</v>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1953" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1953" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1953" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1953" t="n" s="0">
+        <v>1.752756740006E9</v>
+      </c>
+      <c r="F1953" t="n" s="0">
+        <v>1031.5666666666668</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1954" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1954" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1954" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1954" t="n" s="0">
+        <v>1.752756750006E9</v>
+      </c>
+      <c r="F1954" t="n" s="0">
+        <v>995.6166666666667</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1955" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1955" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1955" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1955" t="n" s="0">
+        <v>1.752756760006E9</v>
+      </c>
+      <c r="F1955" t="n" s="0">
+        <v>995.6166666666667</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1956" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1956" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1956" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1956" t="n" s="0">
+        <v>1.752756770006E9</v>
+      </c>
+      <c r="F1956" t="n" s="0">
+        <v>995.6166666666667</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1957" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1957" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1957" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1957" t="n" s="0">
+        <v>1.752756780006E9</v>
+      </c>
+      <c r="F1957" t="n" s="0">
+        <v>959.2833333333334</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1958" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1958" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1958" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1958" t="n" s="0">
+        <v>1.752756790006E9</v>
+      </c>
+      <c r="F1958" t="n" s="0">
+        <v>959.2833333333334</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1959" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1959" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1959" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1959" t="n" s="0">
+        <v>1.752756800006E9</v>
+      </c>
+      <c r="F1959" t="n" s="0">
+        <v>959.2833333333334</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1960" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1960" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1960" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1960" t="n" s="0">
+        <v>1.752756810006E9</v>
+      </c>
+      <c r="F1960" t="n" s="0">
+        <v>933.4966666666667</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1961" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1961" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1961" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1961" t="n" s="0">
+        <v>1.752756820006E9</v>
+      </c>
+      <c r="F1961" t="n" s="0">
+        <v>933.4966666666667</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1962" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1962" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1962" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1962" t="n" s="0">
+        <v>1.752756830006E9</v>
+      </c>
+      <c r="F1962" t="n" s="0">
+        <v>933.4966666666667</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1963" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1963" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1963" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1963" t="n" s="0">
+        <v>1.752756840006E9</v>
+      </c>
+      <c r="F1963" t="n" s="0">
+        <v>932.8833333333332</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1964" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1964" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1964" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1964" t="n" s="0">
+        <v>1.752756850006E9</v>
+      </c>
+      <c r="F1964" t="n" s="0">
+        <v>932.8833333333332</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1965" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1965" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1965" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1965" t="n" s="0">
+        <v>1.752756860006E9</v>
+      </c>
+      <c r="F1965" t="n" s="0">
+        <v>932.8833333333332</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1966" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1966" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1966" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1966" t="n" s="0">
+        <v>1.752756870006E9</v>
+      </c>
+      <c r="F1966" t="n" s="0">
+        <v>907.1500000000001</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1967" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1967" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1967" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1967" t="n" s="0">
+        <v>1.752756880006E9</v>
+      </c>
+      <c r="F1967" t="n" s="0">
+        <v>907.1500000000001</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1968" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1968" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1968" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1968" t="n" s="0">
+        <v>1.752756890006E9</v>
+      </c>
+      <c r="F1968" t="n" s="0">
+        <v>907.1500000000001</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1969" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1969" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1969" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E1969" t="n" s="0">
+        <v>1.752756900006E9</v>
+      </c>
+      <c r="F1969" t="n" s="0">
+        <v>898.28</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1970" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1970" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1970" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E1970" t="n" s="0">
+        <v>1.752756910006E9</v>
+      </c>
+      <c r="F1970" t="n" s="0">
+        <v>898.28</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1971" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1971" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1971" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E1971" t="n" s="0">
+        <v>1.752756920006E9</v>
+      </c>
+      <c r="F1971" t="n" s="0">
+        <v>898.28</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1972" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1972" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1972" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E1972" t="n" s="0">
+        <v>1.752756930006E9</v>
+      </c>
+      <c r="F1972" t="n" s="0">
+        <v>896.8366666666668</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1973" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1973" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1973" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E1973" t="n" s="0">
+        <v>1.752756940006E9</v>
+      </c>
+      <c r="F1973" t="n" s="0">
+        <v>896.8366666666668</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1974" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1974" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1974" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E1974" t="n" s="0">
+        <v>1.752756950006E9</v>
+      </c>
+      <c r="F1974" t="n" s="0">
+        <v>896.8366666666668</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1975" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1975" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1975" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E1975" t="n" s="0">
+        <v>1.752756960006E9</v>
+      </c>
+      <c r="F1975" t="n" s="0">
+        <v>890.2566666666667</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1976" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1976" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1976" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E1976" t="n" s="0">
+        <v>1.752756970006E9</v>
+      </c>
+      <c r="F1976" t="n" s="0">
+        <v>890.2566666666667</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1977" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1977" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1977" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E1977" t="n" s="0">
+        <v>1.752756980006E9</v>
+      </c>
+      <c r="F1977" t="n" s="0">
+        <v>890.2566666666667</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1978" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1978" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1978" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E1978" t="n" s="0">
+        <v>1.752756990006E9</v>
+      </c>
+      <c r="F1978" t="n" s="0">
+        <v>864.13</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1979" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1979" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1979" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E1979" t="n" s="0">
+        <v>1.752757000006E9</v>
+      </c>
+      <c r="F1979" t="n" s="0">
+        <v>864.13</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1980" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1980" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1980" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E1980" t="n" s="0">
+        <v>1.752757010006E9</v>
+      </c>
+      <c r="F1980" t="n" s="0">
+        <v>864.13</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1981" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1981" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1981" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E1981" t="n" s="0">
+        <v>1.752757020006E9</v>
+      </c>
+      <c r="F1981" t="n" s="0">
+        <v>840.9</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1982" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1982" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1982" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E1982" t="n" s="0">
+        <v>1.752756720006E9</v>
+      </c>
+      <c r="F1982" t="n" s="0">
+        <v>2134.466666666667</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1983" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1983" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1983" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E1983" t="n" s="0">
+        <v>1.752756730006E9</v>
+      </c>
+      <c r="F1983" t="n" s="0">
+        <v>2134.466666666667</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1984" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1984" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1984" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E1984" t="n" s="0">
+        <v>1.752756740006E9</v>
+      </c>
+      <c r="F1984" t="n" s="0">
+        <v>2134.466666666667</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1985" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1985" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1985" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E1985" t="n" s="0">
+        <v>1.752756750006E9</v>
+      </c>
+      <c r="F1985" t="n" s="0">
+        <v>2657.0066666666667</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1986" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1986" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1986" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E1986" t="n" s="0">
+        <v>1.752756760006E9</v>
+      </c>
+      <c r="F1986" t="n" s="0">
+        <v>2657.0066666666667</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1987" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1987" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1987" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E1987" t="n" s="0">
+        <v>1.752756770006E9</v>
+      </c>
+      <c r="F1987" t="n" s="0">
+        <v>2657.0066666666667</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1988" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1988" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1988" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E1988" t="n" s="0">
+        <v>1.752756780006E9</v>
+      </c>
+      <c r="F1988" t="n" s="0">
+        <v>3190.6766666666667</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1989" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1989" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1989" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E1989" t="n" s="0">
+        <v>1.752756790006E9</v>
+      </c>
+      <c r="F1989" t="n" s="0">
+        <v>3190.6766666666667</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1990" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1990" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1990" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E1990" t="n" s="0">
+        <v>1.752756800006E9</v>
+      </c>
+      <c r="F1990" t="n" s="0">
+        <v>3190.6766666666667</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1991" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1991" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1991" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E1991" t="n" s="0">
+        <v>1.752756810006E9</v>
+      </c>
+      <c r="F1991" t="n" s="0">
+        <v>3640.1800000000003</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1992" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1992" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1992" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E1992" t="n" s="0">
+        <v>1.752756820006E9</v>
+      </c>
+      <c r="F1992" t="n" s="0">
+        <v>3640.1800000000003</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1993" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1993" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1993" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E1993" t="n" s="0">
+        <v>1.752756830006E9</v>
+      </c>
+      <c r="F1993" t="n" s="0">
+        <v>3640.1800000000003</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1994" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1994" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1994" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E1994" t="n" s="0">
+        <v>1.752756840006E9</v>
+      </c>
+      <c r="F1994" t="n" s="0">
+        <v>4210.066666666667</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1995" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1995" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1995" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E1995" t="n" s="0">
+        <v>1.752756850006E9</v>
+      </c>
+      <c r="F1995" t="n" s="0">
+        <v>4210.066666666667</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1996" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1996" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1996" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E1996" t="n" s="0">
+        <v>1.752756860006E9</v>
+      </c>
+      <c r="F1996" t="n" s="0">
+        <v>4210.066666666667</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1997" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1997" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1997" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E1997" t="n" s="0">
+        <v>1.752756870006E9</v>
+      </c>
+      <c r="F1997" t="n" s="0">
+        <v>4753.796666666666</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1998" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1998" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1998" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E1998" t="n" s="0">
+        <v>1.752756880006E9</v>
+      </c>
+      <c r="F1998" t="n" s="0">
+        <v>4753.796666666666</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B1999" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C1999" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D1999" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E1999" t="n" s="0">
+        <v>1.752756890006E9</v>
+      </c>
+      <c r="F1999" t="n" s="0">
+        <v>4753.796666666666</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2000" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2000" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2000" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E2000" t="n" s="0">
+        <v>1.752756900006E9</v>
+      </c>
+      <c r="F2000" t="n" s="0">
+        <v>5033.69</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2001" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2001" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2001" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E2001" t="n" s="0">
+        <v>1.752756910006E9</v>
+      </c>
+      <c r="F2001" t="n" s="0">
+        <v>5033.69</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2002" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2002" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2002" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E2002" t="n" s="0">
+        <v>1.752756920006E9</v>
+      </c>
+      <c r="F2002" t="n" s="0">
+        <v>5033.69</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2003" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2003" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2003" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E2003" t="n" s="0">
+        <v>1.752756930006E9</v>
+      </c>
+      <c r="F2003" t="n" s="0">
+        <v>4553.043333333334</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2004" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2004" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2004" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E2004" t="n" s="0">
+        <v>1.752756940006E9</v>
+      </c>
+      <c r="F2004" t="n" s="0">
+        <v>4553.043333333334</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2005" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2005" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2005" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E2005" t="n" s="0">
+        <v>1.752756950006E9</v>
+      </c>
+      <c r="F2005" t="n" s="0">
+        <v>4553.043333333334</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2006" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2006" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2006" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E2006" t="n" s="0">
+        <v>1.752756960006E9</v>
+      </c>
+      <c r="F2006" t="n" s="0">
+        <v>4294.639999999999</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2007" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2007" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2007" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E2007" t="n" s="0">
+        <v>1.752756970006E9</v>
+      </c>
+      <c r="F2007" t="n" s="0">
+        <v>4294.639999999999</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2008" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2008" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2008" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E2008" t="n" s="0">
+        <v>1.752756980006E9</v>
+      </c>
+      <c r="F2008" t="n" s="0">
+        <v>4294.639999999999</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2009" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2009" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2009" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E2009" t="n" s="0">
+        <v>1.752756990006E9</v>
+      </c>
+      <c r="F2009" t="n" s="0">
+        <v>4218.806666666666</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2010" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2010" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2010" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E2010" t="n" s="0">
+        <v>1.752757000006E9</v>
+      </c>
+      <c r="F2010" t="n" s="0">
+        <v>4218.806666666666</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2011" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2011" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2011" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E2011" t="n" s="0">
+        <v>1.752757010006E9</v>
+      </c>
+      <c r="F2011" t="n" s="0">
+        <v>4218.806666666666</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2012" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2012" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="D2012" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E2012" t="n" s="0">
+        <v>1.752757020006E9</v>
+      </c>
+      <c r="F2012" t="n" s="0">
+        <v>4132.75</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2013" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2013" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2013" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E2013" t="n" s="0">
+        <v>1.752757088292E9</v>
+      </c>
+      <c r="F2013" t="n" s="0">
+        <v>869.8799999999999</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2014" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2014" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2014" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2014" t="n" s="0">
+        <v>1.752757098292E9</v>
+      </c>
+      <c r="F2014" t="n" s="0">
+        <v>869.8799999999999</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2015" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2015" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2015" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E2015" t="n" s="0">
+        <v>1.752757108292E9</v>
+      </c>
+      <c r="F2015" t="n" s="0">
+        <v>854.52</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2016" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2016" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2016" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E2016" t="n" s="0">
+        <v>1.752757118292E9</v>
+      </c>
+      <c r="F2016" t="n" s="0">
+        <v>854.52</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2017" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2017" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2017" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E2017" t="n" s="0">
+        <v>1.752757128292E9</v>
+      </c>
+      <c r="F2017" t="n" s="0">
+        <v>854.52</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2018" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2018" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2018" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E2018" t="n" s="0">
+        <v>1.752757138292E9</v>
+      </c>
+      <c r="F2018" t="n" s="0">
+        <v>839.8333333333334</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2019" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2019" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2019" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E2019" t="n" s="0">
+        <v>1.752757148292E9</v>
+      </c>
+      <c r="F2019" t="n" s="0">
+        <v>839.8333333333334</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2020" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2020" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2020" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E2020" t="n" s="0">
+        <v>1.752757158292E9</v>
+      </c>
+      <c r="F2020" t="n" s="0">
+        <v>839.8333333333334</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2021" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2021" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2021" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E2021" t="n" s="0">
+        <v>1.752757168292E9</v>
+      </c>
+      <c r="F2021" t="n" s="0">
+        <v>814.3400000000001</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2022" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2022" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2022" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E2022" t="n" s="0">
+        <v>1.752757178292E9</v>
+      </c>
+      <c r="F2022" t="n" s="0">
+        <v>814.3400000000001</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2023" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2023" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2023" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E2023" t="n" s="0">
+        <v>1.752757188292E9</v>
+      </c>
+      <c r="F2023" t="n" s="0">
+        <v>814.3400000000001</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2024" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2024" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2024" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E2024" t="n" s="0">
+        <v>1.752757198292E9</v>
+      </c>
+      <c r="F2024" t="n" s="0">
+        <v>808.2733333333333</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2025" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2025" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2025" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E2025" t="n" s="0">
+        <v>1.752757208292E9</v>
+      </c>
+      <c r="F2025" t="n" s="0">
+        <v>808.2733333333333</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2026" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2026" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2026" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E2026" t="n" s="0">
+        <v>1.752757218292E9</v>
+      </c>
+      <c r="F2026" t="n" s="0">
+        <v>808.2733333333333</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2027" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2027" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2027" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E2027" t="n" s="0">
+        <v>1.752757228292E9</v>
+      </c>
+      <c r="F2027" t="n" s="0">
+        <v>804.2233333333334</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2028" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2028" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2028" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E2028" t="n" s="0">
+        <v>1.752757238292E9</v>
+      </c>
+      <c r="F2028" t="n" s="0">
+        <v>804.2233333333334</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2029" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2029" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2029" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E2029" t="n" s="0">
+        <v>1.752757248292E9</v>
+      </c>
+      <c r="F2029" t="n" s="0">
+        <v>804.2233333333334</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2030" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2030" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2030" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E2030" t="n" s="0">
+        <v>1.752757258292E9</v>
+      </c>
+      <c r="F2030" t="n" s="0">
+        <v>825.7766666666668</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2031" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2031" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2031" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E2031" t="n" s="0">
+        <v>1.752757268292E9</v>
+      </c>
+      <c r="F2031" t="n" s="0">
+        <v>825.7766666666668</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2032" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2032" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2032" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E2032" t="n" s="0">
+        <v>1.752757278292E9</v>
+      </c>
+      <c r="F2032" t="n" s="0">
+        <v>825.7766666666668</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2033" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2033" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2033" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E2033" t="n" s="0">
+        <v>1.752757288292E9</v>
+      </c>
+      <c r="F2033" t="n" s="0">
+        <v>846.9766666666668</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2034" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2034" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2034" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E2034" t="n" s="0">
+        <v>1.752757298292E9</v>
+      </c>
+      <c r="F2034" t="n" s="0">
+        <v>846.9766666666668</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2035" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2035" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2035" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E2035" t="n" s="0">
+        <v>1.752757308292E9</v>
+      </c>
+      <c r="F2035" t="n" s="0">
+        <v>846.9766666666668</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2036" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2036" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2036" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E2036" t="n" s="0">
+        <v>1.752757318292E9</v>
+      </c>
+      <c r="F2036" t="n" s="0">
+        <v>849.5033333333333</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2037" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2037" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2037" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E2037" t="n" s="0">
+        <v>1.752757328292E9</v>
+      </c>
+      <c r="F2037" t="n" s="0">
+        <v>849.5033333333333</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2038" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2038" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2038" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E2038" t="n" s="0">
+        <v>1.752757338292E9</v>
+      </c>
+      <c r="F2038" t="n" s="0">
+        <v>849.5033333333333</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2039" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2039" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2039" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E2039" t="n" s="0">
+        <v>1.752757348292E9</v>
+      </c>
+      <c r="F2039" t="n" s="0">
+        <v>827.6700000000003</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2040" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2040" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2040" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E2040" t="n" s="0">
+        <v>1.752757358292E9</v>
+      </c>
+      <c r="F2040" t="n" s="0">
+        <v>827.6700000000003</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2041" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2041" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2041" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E2041" t="n" s="0">
+        <v>1.752757368292E9</v>
+      </c>
+      <c r="F2041" t="n" s="0">
+        <v>827.6700000000003</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2042" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2042" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2042" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E2042" t="n" s="0">
+        <v>1.752757378292E9</v>
+      </c>
+      <c r="F2042" t="n" s="0">
+        <v>818.0733333333334</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2043" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2043" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2043" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E2043" t="n" s="0">
+        <v>1.752757388292E9</v>
+      </c>
+      <c r="F2043" t="n" s="0">
+        <v>818.0733333333334</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2044" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2044" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2044" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="E2044" t="n" s="0">
+        <v>1.752757088292E9</v>
+      </c>
+      <c r="F2044" t="n" s="0">
+        <v>3290.710000000001</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2045" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2045" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2045" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2045" t="n" s="0">
+        <v>1.752757098292E9</v>
+      </c>
+      <c r="F2045" t="n" s="0">
+        <v>3290.710000000001</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2046" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2046" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2046" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E2046" t="n" s="0">
+        <v>1.752757108292E9</v>
+      </c>
+      <c r="F2046" t="n" s="0">
+        <v>2896.433333333333</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2047" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2047" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2047" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E2047" t="n" s="0">
+        <v>1.752757118292E9</v>
+      </c>
+      <c r="F2047" t="n" s="0">
+        <v>2896.433333333333</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2048" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2048" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2048" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E2048" t="n" s="0">
+        <v>1.752757128292E9</v>
+      </c>
+      <c r="F2048" t="n" s="0">
+        <v>2896.433333333333</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2049" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2049" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2049" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E2049" t="n" s="0">
+        <v>1.752757138292E9</v>
+      </c>
+      <c r="F2049" t="n" s="0">
+        <v>2824.733333333334</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2050" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2050" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2050" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E2050" t="n" s="0">
+        <v>1.752757148292E9</v>
+      </c>
+      <c r="F2050" t="n" s="0">
+        <v>2824.733333333334</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2051" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2051" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2051" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="E2051" t="n" s="0">
+        <v>1.752757158292E9</v>
+      </c>
+      <c r="F2051" t="n" s="0">
+        <v>2824.733333333334</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2052" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2052" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2052" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E2052" t="n" s="0">
+        <v>1.752757168292E9</v>
+      </c>
+      <c r="F2052" t="n" s="0">
+        <v>2738.4266666666676</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2053" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2053" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2053" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E2053" t="n" s="0">
+        <v>1.752757178292E9</v>
+      </c>
+      <c r="F2053" t="n" s="0">
+        <v>2738.4266666666676</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2054" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2054" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2054" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E2054" t="n" s="0">
+        <v>1.752757188292E9</v>
+      </c>
+      <c r="F2054" t="n" s="0">
+        <v>2738.4266666666676</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2055" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2055" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2055" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E2055" t="n" s="0">
+        <v>1.752757198292E9</v>
+      </c>
+      <c r="F2055" t="n" s="0">
+        <v>3014.036666666667</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2056" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2056" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2056" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E2056" t="n" s="0">
+        <v>1.752757208292E9</v>
+      </c>
+      <c r="F2056" t="n" s="0">
+        <v>3014.036666666667</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2057" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2057" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2057" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="E2057" t="n" s="0">
+        <v>1.752757218292E9</v>
+      </c>
+      <c r="F2057" t="n" s="0">
+        <v>3014.036666666667</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2058" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2058" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2058" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="E2058" t="n" s="0">
+        <v>1.752757228292E9</v>
+      </c>
+      <c r="F2058" t="n" s="0">
+        <v>3183.1233333333334</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2059" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2059" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2059" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E2059" t="n" s="0">
+        <v>1.752757238292E9</v>
+      </c>
+      <c r="F2059" t="n" s="0">
+        <v>3183.1233333333334</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2060" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2060" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2060" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E2060" t="n" s="0">
+        <v>1.752757248292E9</v>
+      </c>
+      <c r="F2060" t="n" s="0">
+        <v>3183.1233333333334</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2061" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2061" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2061" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E2061" t="n" s="0">
+        <v>1.752757258292E9</v>
+      </c>
+      <c r="F2061" t="n" s="0">
+        <v>3152.686666666667</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2062" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2062" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2062" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="E2062" t="n" s="0">
+        <v>1.752757268292E9</v>
+      </c>
+      <c r="F2062" t="n" s="0">
+        <v>3152.686666666667</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2063" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2063" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2063" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E2063" t="n" s="0">
+        <v>1.752757278292E9</v>
+      </c>
+      <c r="F2063" t="n" s="0">
+        <v>3152.686666666667</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2064" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2064" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2064" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="E2064" t="n" s="0">
+        <v>1.752757288292E9</v>
+      </c>
+      <c r="F2064" t="n" s="0">
+        <v>3215.14</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2065" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2065" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2065" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="E2065" t="n" s="0">
+        <v>1.752757298292E9</v>
+      </c>
+      <c r="F2065" t="n" s="0">
+        <v>3215.14</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2066" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2066" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2066" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E2066" t="n" s="0">
+        <v>1.752757308292E9</v>
+      </c>
+      <c r="F2066" t="n" s="0">
+        <v>3215.14</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2067" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2067" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2067" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="E2067" t="n" s="0">
+        <v>1.752757318292E9</v>
+      </c>
+      <c r="F2067" t="n" s="0">
+        <v>3599.243333333334</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2068" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2068" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2068" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="E2068" t="n" s="0">
+        <v>1.752757328292E9</v>
+      </c>
+      <c r="F2068" t="n" s="0">
+        <v>3599.243333333334</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2069" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2069" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2069" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="E2069" t="n" s="0">
+        <v>1.752757338292E9</v>
+      </c>
+      <c r="F2069" t="n" s="0">
+        <v>3599.243333333334</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2070" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2070" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2070" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="E2070" t="n" s="0">
+        <v>1.752757348292E9</v>
+      </c>
+      <c r="F2070" t="n" s="0">
+        <v>4099.833333333333</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2071" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2071" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2071" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="E2071" t="n" s="0">
+        <v>1.752757358292E9</v>
+      </c>
+      <c r="F2071" t="n" s="0">
+        <v>4099.833333333333</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2072" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2072" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2072" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="E2072" t="n" s="0">
+        <v>1.752757368292E9</v>
+      </c>
+      <c r="F2072" t="n" s="0">
+        <v>4099.833333333333</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2073" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2073" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2073" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="E2073" t="n" s="0">
+        <v>1.752757378292E9</v>
+      </c>
+      <c r="F2073" t="n" s="0">
+        <v>4363.466666666666</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B2074" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C2074" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="D2074" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E2074" t="n" s="0">
+        <v>1.752757388292E9</v>
+      </c>
+      <c r="F2074" t="n" s="0">
+        <v>4363.466666666666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
